--- a/Recipe_Database_Corrected.xlsx
+++ b/Recipe_Database_Corrected.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taiyenwu/Downloads/Chef Tai/github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA81349-ECC9-894E-81B0-736306B55615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC604B5-F201-4E4A-971B-6F1693738B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recipes" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="518">
   <si>
     <t>RecipeID</t>
   </si>
@@ -490,18 +490,6 @@
     <t>將烤模放入烤箱，以170°C烘烤約22分鐘。</t>
   </si>
   <si>
-    <t>將奶油、檸檬汁、糖和雞蛋混合攪拌均勻，表面的氣泡可用餐巾紙吸附去除。</t>
-  </si>
-  <si>
-    <t>將攪拌好的餡料倒入烤好的餅皮模具中。</t>
-  </si>
-  <si>
-    <t>將模具再次放入烤箱，以170°C烘烤約10分鐘。</t>
-  </si>
-  <si>
-    <t>烤好後，刨上檸檬屑，並用喜歡的水果裝飾。</t>
-  </si>
-  <si>
     <t>Grease the baking mold with butter and line it with parchment paper.</t>
   </si>
   <si>
@@ -509,18 +497,6 @@
   </si>
   <si>
     <t>Bake in the oven at 170°C (340°F) for about 22 minutes.</t>
-  </si>
-  <si>
-    <t>Mix butter, lemon juice, sugar, and eggs until well combined. Remove any surface bubbles by dabbing with a paper towel.</t>
-  </si>
-  <si>
-    <t>Pour the filling into the baked crust in the mold.</t>
-  </si>
-  <si>
-    <t>Bake again in the oven at 170°C (340°F) for about 10 minutes.</t>
-  </si>
-  <si>
-    <t>After baking, sprinkle with lemon zest and decorate with your favorite fruits.</t>
   </si>
   <si>
     <t>CycleTime</t>
@@ -1616,13 +1592,37 @@
   </si>
   <si>
     <t>To assemble, place the hot dog into the bun, top with the sautéed onions and peppers, then add ketchup and mustard to taste. Enjoy!</t>
+  </si>
+  <si>
+    <t>將檸檬汁、糖、蛋黃和全蛋混合，攪拌均勻。</t>
+  </si>
+  <si>
+    <t>隔水加熱方式烹煮，將溫度控制在約 80°C（176°F），注意不要煮滾。</t>
+  </si>
+  <si>
+    <t>將奶油加入並攪拌至完全融合，然後將餡料倒入已烤好的餅皮模具中。</t>
+  </si>
+  <si>
+    <t>用刨絲器刨一些檸檬皮，稍微降溫後，放入冷凍數小時即可食用。</t>
+  </si>
+  <si>
+    <t>Combine lemon juice, sugar, egg yolks, and whole eggs, and mix until smooth.</t>
+  </si>
+  <si>
+    <t>Add butter and stir until fully incorporated, then pour the filling into the pre-baked tart shells.</t>
+  </si>
+  <si>
+    <t>Cook over a double boiler, keeping the temperature around 80°C (175°F), being careful not to let it boil.</t>
+  </si>
+  <si>
+    <t>Grate some lemon zest over the filling, let it cool slightly, then freeze for a few hours before serving.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1669,6 +1669,12 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1719,7 +1725,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1750,6 +1756,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2283,7 +2290,7 @@
         <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>128</v>
@@ -2300,22 +2307,22 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B7" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E7" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>128</v>
@@ -2332,16 +2339,16 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B8" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C8" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D8" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -2353,7 +2360,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>128</v>
@@ -2370,31 +2377,31 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B9" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D9" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E9" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="G9">
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>131</v>
@@ -2405,25 +2412,25 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B10" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C10" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="D10" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="G10">
         <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>128</v>
@@ -2440,22 +2447,22 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B11" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C11" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="D11" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E11" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>128</v>
@@ -2464,24 +2471,24 @@
         <v>140</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B12" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C12" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D12" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -2493,7 +2500,7 @@
         <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>127</v>
@@ -2510,22 +2517,22 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B13" t="s">
+        <v>484</v>
+      </c>
+      <c r="C13" t="s">
+        <v>485</v>
+      </c>
+      <c r="D13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" t="s">
+        <v>251</v>
+      </c>
+      <c r="H13" t="s">
         <v>492</v>
-      </c>
-      <c r="C13" t="s">
-        <v>493</v>
-      </c>
-      <c r="D13" t="s">
-        <v>371</v>
-      </c>
-      <c r="E13" t="s">
-        <v>259</v>
-      </c>
-      <c r="H13" t="s">
-        <v>500</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>128</v>
@@ -2832,10 +2839,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>48</v>
@@ -2846,10 +2853,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>60</v>
@@ -2860,24 +2867,24 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>48</v>
@@ -2888,10 +2895,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>48</v>
@@ -2902,24 +2909,24 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>48</v>
@@ -2930,10 +2937,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>48</v>
@@ -2944,10 +2951,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>42</v>
@@ -2958,10 +2965,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>45</v>
@@ -2972,10 +2979,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>48</v>
@@ -2992,7 +2999,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="8.83203125" style="5"/>
@@ -3131,7 +3138,7 @@
         <v>72</v>
       </c>
       <c r="D7" s="5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>67</v>
@@ -3182,19 +3189,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D10" s="5">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F10" s="5" t="b">
         <v>0</v>
@@ -3208,10 +3215,10 @@
         <v>47</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D11" s="5">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>67</v>
@@ -3228,10 +3235,10 @@
         <v>47</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D12" s="5">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>67</v>
@@ -3248,10 +3255,10 @@
         <v>47</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D13" s="5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>67</v>
@@ -3268,10 +3275,10 @@
         <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>67</v>
@@ -3288,13 +3295,13 @@
         <v>47</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D15" s="5">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F15" s="5" t="b">
         <v>0</v>
@@ -3308,13 +3315,13 @@
         <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D16" s="5">
-        <v>0.5</v>
+        <v>85</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="b">
         <v>0</v>
@@ -3328,10 +3335,10 @@
         <v>47</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D17" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>75</v>
@@ -3342,19 +3349,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D18" s="5">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F18" s="5" t="b">
         <v>0</v>
@@ -3368,10 +3375,10 @@
         <v>50</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D19" s="5">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>67</v>
@@ -3388,10 +3395,10 @@
         <v>50</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>67</v>
@@ -3405,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D21" s="5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>67</v>
@@ -3428,10 +3435,10 @@
         <v>53</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>67</v>
@@ -3448,10 +3455,10 @@
         <v>53</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D23" s="5">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>67</v>
@@ -3468,10 +3475,10 @@
         <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D24" s="5">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>67</v>
@@ -3488,16 +3495,16 @@
         <v>53</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="D25" s="5">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F25" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -3508,16 +3515,16 @@
         <v>53</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="D26" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F26" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -3528,10 +3535,10 @@
         <v>53</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D27" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>75</v>
@@ -3548,36 +3555,36 @@
         <v>53</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F28" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="D29" s="5">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="F29" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -3588,10 +3595,10 @@
         <v>56</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D30" s="5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>67</v>
@@ -3608,10 +3615,10 @@
         <v>56</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D31" s="5">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>67</v>
@@ -3628,10 +3635,10 @@
         <v>56</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D32" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>67</v>
@@ -3648,10 +3655,10 @@
         <v>56</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D33" s="5">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>67</v>
@@ -3668,13 +3675,13 @@
         <v>56</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D34" s="5">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F34" s="5" t="b">
         <v>0</v>
@@ -3685,16 +3692,16 @@
         <v>27</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D35" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F35" s="5" t="b">
         <v>0</v>
@@ -3708,10 +3715,10 @@
         <v>57</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D36" s="5">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>67</v>
@@ -3728,13 +3735,13 @@
         <v>57</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D37" s="5">
-        <v>0.5</v>
+        <v>30</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F37" s="5" t="b">
         <v>0</v>
@@ -3748,13 +3755,13 @@
         <v>57</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D38" s="5">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F38" s="5" t="b">
         <v>0</v>
@@ -3768,10 +3775,10 @@
         <v>57</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D39" s="5">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>67</v>
@@ -3782,19 +3789,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D40" s="5">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F40" s="5" t="b">
         <v>0</v>
@@ -3808,13 +3815,13 @@
         <v>58</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D41" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F41" s="5" t="b">
         <v>0</v>
@@ -3828,10 +3835,10 @@
         <v>58</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D42" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>67</v>
@@ -3848,10 +3855,10 @@
         <v>58</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D43" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>67</v>
@@ -3868,7 +3875,7 @@
         <v>58</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -3885,16 +3892,16 @@
         <v>33</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D45" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F45" s="5" t="b">
         <v>0</v>
@@ -3908,13 +3915,13 @@
         <v>59</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D46" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F46" s="5" t="b">
         <v>0</v>
@@ -3928,13 +3935,13 @@
         <v>59</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D47" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="F47" s="5" t="b">
         <v>0</v>
@@ -3948,10 +3955,10 @@
         <v>59</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D48" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>92</v>
@@ -3968,10 +3975,10 @@
         <v>59</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>92</v>
@@ -3988,13 +3995,13 @@
         <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D50" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F50" s="5" t="b">
         <v>0</v>
@@ -4008,13 +4015,13 @@
         <v>59</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D51" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F51" s="5" t="b">
         <v>0</v>
@@ -4022,19 +4029,19 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>255</v>
+        <v>33</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>263</v>
+        <v>59</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>277</v>
+        <v>96</v>
       </c>
       <c r="D52" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F52" s="5" t="b">
         <v>0</v>
@@ -4042,16 +4049,16 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>263</v>
-      </c>
       <c r="C53" s="5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D53" s="5">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>75</v>
@@ -4059,20 +4066,16 @@
       <c r="F53" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>263</v>
-      </c>
       <c r="C54" s="5" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D54" s="5">
         <v>0.2</v>
@@ -4090,16 +4093,16 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>263</v>
-      </c>
       <c r="C55" s="5" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="D55" s="5">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>75</v>
@@ -4114,39 +4117,43 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>263</v>
-      </c>
       <c r="C56" s="5" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D56" s="5">
         <v>4</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>284</v>
+        <v>75</v>
       </c>
       <c r="F56" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>264</v>
-      </c>
       <c r="C57" s="5" t="s">
-        <v>94</v>
+        <v>273</v>
       </c>
       <c r="D57" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>92</v>
+        <v>276</v>
       </c>
       <c r="F57" s="5" t="b">
         <v>0</v>
@@ -4154,13 +4161,13 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>279</v>
+        <v>94</v>
       </c>
       <c r="D58" s="5">
         <v>3</v>
@@ -4174,19 +4181,19 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D59" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="F59" s="5" t="b">
         <v>0</v>
@@ -4194,13 +4201,13 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D60" s="5">
         <v>1</v>
@@ -4209,18 +4216,18 @@
         <v>67</v>
       </c>
       <c r="F60" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>87</v>
+        <v>272</v>
       </c>
       <c r="D61" s="5">
         <v>1</v>
@@ -4229,64 +4236,64 @@
         <v>67</v>
       </c>
       <c r="F61" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>301</v>
+        <v>87</v>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F62" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="D63" s="5">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F63" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D64" s="5">
-        <v>0.5</v>
+        <v>400</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F64" s="5" t="b">
         <v>0</v>
@@ -4294,19 +4301,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="D65" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F65" s="5" t="b">
         <v>0</v>
@@ -4314,13 +4321,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
@@ -4334,13 +4341,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
@@ -4354,19 +4361,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D68" s="5">
         <v>1</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F68" s="5" t="b">
         <v>0</v>
@@ -4374,19 +4381,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>309</v>
+        <v>247</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>313</v>
+        <v>74</v>
       </c>
       <c r="D69" s="5">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F69" s="5" t="b">
         <v>0</v>
@@ -4394,19 +4401,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D70" s="5">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F70" s="5" t="b">
         <v>0</v>
@@ -4414,19 +4421,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D71" s="5">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>328</v>
+        <v>75</v>
       </c>
       <c r="F71" s="5" t="b">
         <v>0</v>
@@ -4434,19 +4441,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="D72" s="5">
         <v>0.5</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="F72" s="5" t="b">
         <v>0</v>
@@ -4454,16 +4461,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>315</v>
+        <v>268</v>
       </c>
       <c r="D73" s="5">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>75</v>
@@ -4474,16 +4481,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D74" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>75</v>
@@ -4494,19 +4501,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D75" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>327</v>
+        <v>75</v>
       </c>
       <c r="F75" s="5" t="b">
         <v>0</v>
@@ -4514,19 +4521,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D76" s="5">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>67</v>
+        <v>319</v>
       </c>
       <c r="F76" s="5" t="b">
         <v>0</v>
@@ -4534,53 +4541,53 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F77" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>70</v>
+        <v>317</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F78" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D79" s="5">
         <v>1</v>
@@ -4594,10 +4601,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>346</v>
+        <v>301</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>87</v>
@@ -4614,13 +4621,13 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D81" s="5">
         <v>1</v>
@@ -4634,13 +4641,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>283</v>
+        <v>70</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
@@ -4654,19 +4661,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="D83" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F83" s="5" t="b">
         <v>0</v>
@@ -4674,16 +4681,16 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="D84" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>75</v>
@@ -4694,16 +4701,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="D85" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>75</v>
@@ -4714,16 +4721,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>353</v>
+        <v>268</v>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>75</v>
@@ -4734,16 +4741,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D87" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>75</v>
@@ -4754,16 +4761,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>75</v>
@@ -4774,16 +4781,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="D89" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>75</v>
@@ -4794,16 +4801,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>353</v>
+        <v>268</v>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>75</v>
@@ -4814,16 +4821,16 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="D91" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>75</v>
@@ -4834,16 +4841,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B92" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B92" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C92" s="5" t="s">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="D92" s="5">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>75</v>
@@ -4854,16 +4861,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C93" s="5" t="s">
-        <v>426</v>
+        <v>268</v>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>75</v>
@@ -4874,19 +4881,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B94" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C94" s="5" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="D94" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F94" s="5" t="b">
         <v>0</v>
@@ -4894,16 +4901,16 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B95" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C95" s="5" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D95" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>67</v>
@@ -4914,19 +4921,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B96" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C96" s="5" t="s">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="D96" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F96" s="5" t="b">
         <v>0</v>
@@ -4934,13 +4941,13 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B97" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C97" s="5" t="s">
-        <v>282</v>
+        <v>90</v>
       </c>
       <c r="D97" s="5">
         <v>2</v>
@@ -4954,19 +4961,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B98" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B98" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C98" s="5" t="s">
-        <v>87</v>
+        <v>274</v>
       </c>
       <c r="D98" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F98" s="5" t="b">
         <v>0</v>
@@ -4974,13 +4981,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B99" s="5" t="s">
-        <v>376</v>
-      </c>
       <c r="C99" s="5" t="s">
-        <v>283</v>
+        <v>87</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
@@ -4994,19 +5001,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>386</v>
-      </c>
       <c r="C100" s="5" t="s">
-        <v>401</v>
+        <v>275</v>
       </c>
       <c r="D100" s="5">
         <v>1</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>405</v>
+        <v>67</v>
       </c>
       <c r="F100" s="5" t="b">
         <v>0</v>
@@ -5014,19 +5021,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D101" s="5">
         <v>1</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F101" s="5" t="b">
         <v>0</v>
@@ -5034,19 +5041,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D102" s="5">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>67</v>
+        <v>397</v>
       </c>
       <c r="F102" s="5" t="b">
         <v>0</v>
@@ -5054,19 +5061,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D103" s="5">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>406</v>
+        <v>67</v>
       </c>
       <c r="F103" s="5" t="b">
         <v>0</v>
@@ -5074,19 +5081,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D104" s="5">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>75</v>
+        <v>398</v>
       </c>
       <c r="F104" s="5" t="b">
         <v>0</v>
@@ -5094,16 +5101,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="D105" s="5">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E105" s="5" t="s">
         <v>75</v>
@@ -5114,13 +5121,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>315</v>
+        <v>395</v>
       </c>
       <c r="D106" s="5">
         <v>1</v>
@@ -5134,19 +5141,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>404</v>
+        <v>307</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F107" s="5" t="b">
         <v>0</v>
@@ -5154,93 +5161,93 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>396</v>
       </c>
       <c r="D108" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F108" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D109" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F109" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D110" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F110" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="D111" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F111" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D112" s="5">
         <v>6</v>
@@ -5249,38 +5256,38 @@
         <v>75</v>
       </c>
       <c r="F112" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>89</v>
+        <v>401</v>
       </c>
       <c r="D113" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F113" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D114" s="5">
         <v>1</v>
@@ -5294,16 +5301,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>454</v>
+        <v>372</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>462</v>
+        <v>378</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D115" s="5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>67</v>
@@ -5314,16 +5321,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B116" s="5" t="s">
-        <v>462</v>
-      </c>
       <c r="C116" s="5" t="s">
-        <v>459</v>
+        <v>66</v>
       </c>
       <c r="D116" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>67</v>
@@ -5334,16 +5341,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>462</v>
-      </c>
       <c r="C117" s="5" t="s">
-        <v>77</v>
+        <v>451</v>
       </c>
       <c r="D117" s="5">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>67</v>
@@ -5354,56 +5361,56 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>462</v>
-      </c>
       <c r="C118" s="5" t="s">
-        <v>464</v>
+        <v>77</v>
       </c>
       <c r="D118" s="5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F118" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B119" s="5" t="s">
-        <v>462</v>
-      </c>
       <c r="C119" s="5" t="s">
-        <v>70</v>
+        <v>456</v>
       </c>
       <c r="D119" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F119" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B120" s="5" t="s">
-        <v>462</v>
-      </c>
       <c r="C120" s="5" t="s">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="D120" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>67</v>
@@ -5414,19 +5421,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B121" s="5" t="s">
-        <v>462</v>
-      </c>
       <c r="C121" s="5" t="s">
-        <v>74</v>
+        <v>452</v>
       </c>
       <c r="D121" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F121" s="5" t="b">
         <v>0</v>
@@ -5434,16 +5441,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B122" s="5" t="s">
-        <v>463</v>
-      </c>
       <c r="C122" s="5" t="s">
-        <v>458</v>
+        <v>74</v>
       </c>
       <c r="D122" s="5">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>75</v>
@@ -5454,19 +5461,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>69</v>
+        <v>450</v>
       </c>
       <c r="D123" s="5">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F123" s="5" t="b">
         <v>0</v>
@@ -5474,19 +5481,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D124" s="5">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F124" s="5" t="b">
         <v>0</v>
@@ -5494,16 +5501,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="C125" t="s">
-        <v>495</v>
+        <v>455</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="D125" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>75</v>
@@ -5514,13 +5521,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C126" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="D126" s="5">
         <v>2</v>
@@ -5534,16 +5541,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C127" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="D127" s="5">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>75</v>
@@ -5554,13 +5561,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C128" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D128" s="5">
         <v>0.25</v>
@@ -5574,13 +5581,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C129" t="s">
-        <v>276</v>
+        <v>490</v>
       </c>
       <c r="D129" s="5">
         <v>0.25</v>
@@ -5594,53 +5601,53 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C130" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="D130" s="5">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F130" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C131" t="s">
-        <v>87</v>
+        <v>293</v>
       </c>
       <c r="D131" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F131" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C132" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D132" s="5">
         <v>1</v>
@@ -5654,13 +5661,13 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C133" t="s">
-        <v>499</v>
+        <v>94</v>
       </c>
       <c r="D133" s="5">
         <v>1</v>
@@ -5674,13 +5681,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C134" t="s">
         <v>491</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="D134" s="5">
         <v>1</v>
@@ -5689,6 +5696,26 @@
         <v>67</v>
       </c>
       <c r="F134" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D135" s="5">
+        <v>1</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F135" s="5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5872,10 +5899,10 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -5952,34 +5979,34 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -6000,10 +6027,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -6012,58 +6039,58 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B40" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B41" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -6072,40 +6099,40 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B45" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B46" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B48" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="G48" s="2"/>
       <c r="I48" s="4"/>
@@ -6113,236 +6140,236 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B52" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B53" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B58" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B62" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B63" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B69" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B70" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B72" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B73" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B74" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B75" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -6388,10 +6415,10 @@
         <v>124</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6408,7 +6435,7 @@
         <v>43</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>146</v>
@@ -6434,7 +6461,7 @@
         <v>43</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>147</v>
@@ -6460,7 +6487,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>148</v>
@@ -6486,7 +6513,7 @@
         <v>43</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>149</v>
@@ -6512,10 +6539,10 @@
         <v>46</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>157</v>
+        <v>514</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>150</v>
+        <v>510</v>
       </c>
       <c r="G6" s="4">
         <v>5</v>
@@ -6538,10 +6565,10 @@
         <v>46</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>158</v>
+        <v>516</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>151</v>
+        <v>511</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
@@ -6564,10 +6591,10 @@
         <v>46</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>159</v>
+        <v>515</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>152</v>
+        <v>512</v>
       </c>
       <c r="G8" s="4">
         <v>10</v>
@@ -6590,10 +6617,10 @@
         <v>144</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>160</v>
+        <v>517</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>153</v>
+        <v>513</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -6616,10 +6643,10 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G10" s="4">
         <v>3</v>
@@ -6642,10 +6669,10 @@
         <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="G11" s="4">
         <v>5</v>
@@ -6668,10 +6695,10 @@
         <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="G12" s="4">
         <v>2</v>
@@ -6694,10 +6721,10 @@
         <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="G13" s="4">
         <v>5</v>
@@ -6720,10 +6747,10 @@
         <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="G14" s="4">
         <v>3</v>
@@ -6746,10 +6773,10 @@
         <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="G15" s="4">
         <v>2</v>
@@ -6772,10 +6799,10 @@
         <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="G16" s="4">
         <v>1</v>
@@ -6798,10 +6825,10 @@
         <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="G17" s="4">
         <v>20</v>
@@ -6824,10 +6851,10 @@
         <v>52</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G18" s="4">
         <v>5</v>
@@ -6850,10 +6877,10 @@
         <v>52</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G19" s="4">
         <v>3</v>
@@ -6876,10 +6903,10 @@
         <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G20" s="4">
         <v>10</v>
@@ -6902,10 +6929,10 @@
         <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G21" s="4">
         <v>1</v>
@@ -6928,10 +6955,10 @@
         <v>55</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G22" s="4">
         <v>3</v>
@@ -6954,10 +6981,10 @@
         <v>55</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G23" s="4">
         <v>1</v>
@@ -6980,10 +7007,10 @@
         <v>55</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G24" s="4">
         <v>1</v>
@@ -7011,10 +7038,10 @@
         <v>55</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F25" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G25" s="4">
         <v>5</v>
@@ -7037,10 +7064,10 @@
         <v>55</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G26" s="4">
         <v>3</v>
@@ -7063,10 +7090,10 @@
         <v>55</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
@@ -7089,10 +7116,10 @@
         <v>55</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G28" s="4">
         <v>65</v>
@@ -7115,10 +7142,10 @@
         <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G29" s="4">
         <v>0</v>
@@ -7141,10 +7168,10 @@
         <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
@@ -7167,10 +7194,10 @@
         <v>43</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G31" s="4">
         <v>3</v>
@@ -7193,10 +7220,10 @@
         <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G32" s="4">
         <v>60</v>
@@ -7219,10 +7246,10 @@
         <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F33" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G33" s="4">
         <v>5</v>
@@ -7245,10 +7272,10 @@
         <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F34" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G34" s="4">
         <v>3</v>
@@ -7271,10 +7298,10 @@
         <v>49</v>
       </c>
       <c r="E35" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F35" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G35" s="4">
         <v>3</v>
@@ -7297,10 +7324,10 @@
         <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="F36" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G36" s="4">
         <v>5</v>
@@ -7323,10 +7350,10 @@
         <v>49</v>
       </c>
       <c r="E37" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F37" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G37" s="4">
         <v>2</v>
@@ -7349,10 +7376,10 @@
         <v>49</v>
       </c>
       <c r="E38" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F38" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G38" s="4">
         <v>25</v>
@@ -7375,10 +7402,10 @@
         <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F39" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G39" s="4">
         <v>10</v>
@@ -7401,10 +7428,10 @@
         <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F40" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="G40" s="4">
         <v>50</v>
@@ -7427,10 +7454,10 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F41" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G41" s="4">
         <v>5</v>
@@ -7453,10 +7480,10 @@
         <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F42" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G42" s="9">
         <v>5</v>
@@ -7479,10 +7506,10 @@
         <v>49</v>
       </c>
       <c r="E43" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F43" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="G43" s="9">
         <v>1</v>
@@ -7493,22 +7520,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B44" s="4">
         <v>1</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E44" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F44" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="G44" s="9">
         <v>5</v>
@@ -7519,22 +7546,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B45" s="4">
         <v>2</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E45" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F45" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G45" s="9">
         <v>5</v>
@@ -7545,22 +7572,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E46" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F46" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="G46" s="9">
         <v>3</v>
@@ -7571,7 +7598,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B47" s="4">
         <v>4</v>
@@ -7583,10 +7610,10 @@
         <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="F47" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G47" s="9">
         <v>2</v>
@@ -7597,7 +7624,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B48" s="4">
         <v>5</v>
@@ -7609,10 +7636,10 @@
         <v>49</v>
       </c>
       <c r="E48" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F48" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="G48" s="9">
         <v>3</v>
@@ -7623,7 +7650,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B49" s="4">
         <v>6</v>
@@ -7635,10 +7662,10 @@
         <v>49</v>
       </c>
       <c r="E49" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F49" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G49" s="9">
         <v>5</v>
@@ -7649,7 +7676,7 @@
     </row>
     <row r="50" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B50" s="4">
         <v>7</v>
@@ -7661,10 +7688,10 @@
         <v>49</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G50" s="9">
         <v>10</v>
@@ -7675,7 +7702,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B51" s="4">
         <v>8</v>
@@ -7687,10 +7714,10 @@
         <v>49</v>
       </c>
       <c r="E51" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F51" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G51" s="9">
         <v>5</v>
@@ -7701,7 +7728,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
@@ -7713,10 +7740,10 @@
         <v>49</v>
       </c>
       <c r="E52" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F52" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="G52" s="9">
         <v>10</v>
@@ -7727,7 +7754,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B53" s="4">
         <v>2</v>
@@ -7739,10 +7766,10 @@
         <v>49</v>
       </c>
       <c r="E53" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F53" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="G53" s="9">
         <v>10</v>
@@ -7753,7 +7780,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B54" s="4">
         <v>3</v>
@@ -7765,10 +7792,10 @@
         <v>49</v>
       </c>
       <c r="E54" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F54" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="G54" s="9">
         <v>5</v>
@@ -7779,7 +7806,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B55" s="4">
         <v>4</v>
@@ -7791,10 +7818,10 @@
         <v>49</v>
       </c>
       <c r="E55" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F55" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="G55" s="9">
         <v>10</v>
@@ -7805,7 +7832,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B56" s="4">
         <v>5</v>
@@ -7817,10 +7844,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F56" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="G56" s="9">
         <v>5</v>
@@ -7831,7 +7858,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B57" s="4">
         <v>6</v>
@@ -7843,10 +7870,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F57" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="G57" s="9">
         <v>1</v>
@@ -7857,7 +7884,7 @@
     </row>
     <row r="58" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B58" s="4">
         <v>7</v>
@@ -7869,10 +7896,10 @@
         <v>49</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="G58" s="9">
         <v>20</v>
@@ -7883,7 +7910,7 @@
     </row>
     <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B59" s="4">
         <v>1</v>
@@ -7895,10 +7922,10 @@
         <v>49</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="G59" s="9">
         <v>10</v>
@@ -7909,7 +7936,7 @@
     </row>
     <row r="60" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B60" s="4">
         <v>2</v>
@@ -7921,10 +7948,10 @@
         <v>49</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="G60" s="9">
         <v>1</v>
@@ -7935,7 +7962,7 @@
     </row>
     <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B61" s="4">
         <v>3</v>
@@ -7947,10 +7974,10 @@
         <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="G61" s="9">
         <v>20</v>
@@ -7961,7 +7988,7 @@
     </row>
     <row r="62" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B62" s="4">
         <v>4</v>
@@ -7973,10 +8000,10 @@
         <v>49</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="G62" s="9">
         <v>1</v>
@@ -7987,7 +8014,7 @@
     </row>
     <row r="63" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B63" s="4">
         <v>1</v>
@@ -7996,13 +8023,13 @@
         <v>60</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="G63" s="9">
         <v>32</v>
@@ -8013,7 +8040,7 @@
     </row>
     <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B64" s="4">
         <v>1</v>
@@ -8025,10 +8052,10 @@
         <v>49</v>
       </c>
       <c r="E64" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="G64" s="9">
         <v>10</v>
@@ -8039,7 +8066,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B65" s="4">
         <v>2</v>
@@ -8051,10 +8078,10 @@
         <v>49</v>
       </c>
       <c r="E65" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="F65" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="G65" s="9">
         <v>5</v>
@@ -8065,7 +8092,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B66" s="4">
         <v>3</v>
@@ -8077,10 +8104,10 @@
         <v>49</v>
       </c>
       <c r="E66" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F66" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="G66" s="9">
         <v>3</v>
@@ -8091,7 +8118,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B67" s="4">
         <v>4</v>
@@ -8103,10 +8130,10 @@
         <v>49</v>
       </c>
       <c r="E67" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="F67" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="G67" s="9">
         <v>3</v>
@@ -8117,7 +8144,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B68" s="4">
         <v>5</v>
@@ -8129,10 +8156,10 @@
         <v>49</v>
       </c>
       <c r="E68" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="F68" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G68" s="9">
         <v>3</v>
@@ -8143,7 +8170,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B69" s="4">
         <v>6</v>
@@ -8155,10 +8182,10 @@
         <v>49</v>
       </c>
       <c r="E69" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="F69" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="G69" s="4">
         <v>1</v>
@@ -8169,7 +8196,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B70" s="4">
         <v>7</v>
@@ -8181,10 +8208,10 @@
         <v>49</v>
       </c>
       <c r="E70" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="F70" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="G70" s="4">
         <v>20</v>
@@ -8195,7 +8222,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B71" s="4">
         <v>8</v>
@@ -8207,10 +8234,10 @@
         <v>49</v>
       </c>
       <c r="E71" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="F71" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -8221,7 +8248,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B72" s="4">
         <v>9</v>
@@ -8233,10 +8260,10 @@
         <v>49</v>
       </c>
       <c r="E72" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F72" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="G72" s="4">
         <v>0</v>
@@ -8247,7 +8274,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B73" s="4">
         <v>10</v>
@@ -8259,10 +8286,10 @@
         <v>49</v>
       </c>
       <c r="E73" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="F73" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="G73" s="4">
         <v>1</v>
@@ -8273,7 +8300,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B74" s="4">
         <v>1</v>
@@ -8285,10 +8312,10 @@
         <v>49</v>
       </c>
       <c r="E74" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="F74" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="G74" s="9">
         <v>50</v>
@@ -8299,7 +8326,7 @@
     </row>
     <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B75" s="4">
         <v>2</v>
@@ -8311,10 +8338,10 @@
         <v>49</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F75" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="G75" s="9">
         <v>10</v>
@@ -8325,7 +8352,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B76" s="4">
         <v>3</v>
@@ -8337,10 +8364,10 @@
         <v>49</v>
       </c>
       <c r="E76" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="F76" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G76" s="9">
         <v>10</v>
@@ -8351,7 +8378,7 @@
     </row>
     <row r="77" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B77" s="4">
         <v>4</v>
@@ -8363,10 +8390,10 @@
         <v>49</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F77" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="G77" s="9">
         <v>10</v>
@@ -8377,7 +8404,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B78" s="4">
         <v>5</v>
@@ -8389,10 +8416,10 @@
         <v>49</v>
       </c>
       <c r="E78" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="F78" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="G78" s="9">
         <v>10</v>
@@ -8403,7 +8430,7 @@
     </row>
     <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B79" s="4">
         <v>6</v>
@@ -8415,10 +8442,10 @@
         <v>49</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="F79" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="G79" s="9">
         <v>1</v>
@@ -8429,7 +8456,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B80" s="4">
         <v>7</v>
@@ -8441,10 +8468,10 @@
         <v>49</v>
       </c>
       <c r="E80" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="F80" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="G80" s="9">
         <v>1</v>
@@ -8455,7 +8482,7 @@
     </row>
     <row r="81" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B81" s="4">
         <v>1</v>
@@ -8467,10 +8494,10 @@
         <v>46</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="G81" s="9">
         <v>5</v>
@@ -8481,7 +8508,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B82" s="4">
         <v>2</v>
@@ -8493,10 +8520,10 @@
         <v>46</v>
       </c>
       <c r="E82" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F82" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="G82" s="9">
         <v>30</v>
@@ -8507,7 +8534,7 @@
     </row>
     <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B83" s="4">
         <v>3</v>
@@ -8519,10 +8546,10 @@
         <v>43</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="F83" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="G83" s="9">
         <v>1</v>
@@ -8533,7 +8560,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B84" s="4">
         <v>4</v>
@@ -8545,10 +8572,10 @@
         <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F84" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="G84" s="9">
         <v>5</v>
@@ -8559,7 +8586,7 @@
     </row>
     <row r="85" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B85" s="4">
         <v>5</v>
@@ -8571,10 +8598,10 @@
         <v>43</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="F85" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G85" s="9">
         <v>1</v>
@@ -8585,7 +8612,7 @@
     </row>
     <row r="86" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B86" s="4">
         <v>6</v>
@@ -8597,10 +8624,10 @@
         <v>43</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="G86" s="9">
         <v>3</v>
@@ -8611,7 +8638,7 @@
     </row>
     <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B87" s="4">
         <v>7</v>
@@ -8623,10 +8650,10 @@
         <v>43</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F87" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="G87" s="9">
         <v>40</v>
@@ -8637,7 +8664,7 @@
     </row>
     <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B88" s="4">
         <v>8</v>
@@ -8649,10 +8676,10 @@
         <v>43</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F88" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="G88" s="9">
         <v>0</v>
@@ -8663,7 +8690,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B89" s="4">
         <v>1</v>
@@ -8675,10 +8702,10 @@
         <v>49</v>
       </c>
       <c r="E89" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="F89" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="G89" s="9">
         <v>3</v>
@@ -8689,7 +8716,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B90" s="4">
         <v>2</v>
@@ -8701,10 +8728,10 @@
         <v>49</v>
       </c>
       <c r="E90" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="F90" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="G90" s="9">
         <v>5</v>
@@ -8715,7 +8742,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B91" s="4">
         <v>3</v>
@@ -8727,10 +8754,10 @@
         <v>49</v>
       </c>
       <c r="E91" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F91" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="G91" s="9">
         <v>1</v>
@@ -8741,7 +8768,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B92" s="4">
         <v>4</v>
@@ -8753,10 +8780,10 @@
         <v>49</v>
       </c>
       <c r="E92" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="F92" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="G92" s="4">
         <v>3</v>
@@ -8767,7 +8794,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B93" s="4">
         <v>5</v>
@@ -8779,10 +8806,10 @@
         <v>49</v>
       </c>
       <c r="E93" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="F93" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="G93" s="4">
         <v>5</v>
@@ -8793,7 +8820,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B94" s="4">
         <v>6</v>
@@ -8805,10 +8832,10 @@
         <v>49</v>
       </c>
       <c r="E94" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F94" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="G94" s="9">
         <v>3</v>
@@ -8825,11 +8852,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BD390-6058-3244-B040-3ECD44D7EDBB}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
     <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -8837,10 +8869,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D1" t="s">
         <v>65</v>
@@ -8851,10 +8883,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -8865,10 +8897,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -8879,10 +8911,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -8893,10 +8925,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -8907,10 +8939,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -8921,10 +8953,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -8935,10 +8967,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -8949,10 +8981,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -8963,10 +8995,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -8977,10 +9009,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -8991,10 +9023,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -9005,10 +9037,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -9019,10 +9051,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -9033,10 +9065,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -9047,10 +9079,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -9061,10 +9093,10 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -9075,10 +9107,10 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -9089,10 +9121,10 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -9103,10 +9135,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C20" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -9117,10 +9149,10 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -9131,10 +9163,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -9145,10 +9177,10 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -9159,10 +9191,10 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -9173,10 +9205,10 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -9187,10 +9219,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C26" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -9201,10 +9233,10 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C27" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -9215,10 +9247,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -9229,10 +9261,10 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -9243,10 +9275,10 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C30" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -9254,13 +9286,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B31" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C31" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -9268,241 +9300,249 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B35" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B36" t="s">
+        <v>321</v>
+      </c>
+      <c r="C36" t="s">
+        <v>322</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B37" t="s">
         <v>166</v>
       </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="C37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B38" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" t="s">
+        <v>356</v>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" t="s">
+        <v>357</v>
+      </c>
+      <c r="C39" t="s">
+        <v>355</v>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B41" t="s">
+        <v>357</v>
+      </c>
+      <c r="C41" t="s">
+        <v>355</v>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" s="14"/>
+    </row>
+    <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B42" t="s">
+        <v>190</v>
+      </c>
+      <c r="C42" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" s="14"/>
+    </row>
+    <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B43" t="s">
+        <v>460</v>
+      </c>
+      <c r="C43" t="s">
+        <v>461</v>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" s="14"/>
+    </row>
+    <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B44" t="s">
         <v>166</v>
       </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B36" t="s">
-        <v>329</v>
-      </c>
-      <c r="C36" t="s">
-        <v>330</v>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B37" t="s">
-        <v>174</v>
-      </c>
-      <c r="C37" t="s">
-        <v>167</v>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B38" t="s">
-        <v>362</v>
-      </c>
-      <c r="C38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B39" t="s">
-        <v>365</v>
-      </c>
-      <c r="C39" t="s">
-        <v>363</v>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B40" t="s">
-        <v>247</v>
-      </c>
-      <c r="C40" t="s">
-        <v>248</v>
-      </c>
-      <c r="D40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="B41" t="s">
-        <v>365</v>
-      </c>
-      <c r="C41" t="s">
-        <v>363</v>
-      </c>
-      <c r="D41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="B42" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" t="s">
-        <v>197</v>
-      </c>
-      <c r="D42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="B43" t="s">
-        <v>468</v>
-      </c>
-      <c r="C43" t="s">
-        <v>469</v>
-      </c>
-      <c r="D43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="B44" t="s">
-        <v>174</v>
-      </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D44" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N44" s="14"/>
+    </row>
+    <row r="45" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B45" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C45" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D45" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N45" s="14"/>
+    </row>
+    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D46" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N46" s="14"/>
+    </row>
+    <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B47" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C47" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D47" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N47" s="14"/>
+    </row>
+    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B48" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D48" t="b">
         <v>0</v>
       </c>
+      <c r="N48" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Recipe_Database_Corrected.xlsx
+++ b/Recipe_Database_Corrected.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taiyenwu/Downloads/Chef Tai/github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC604B5-F201-4E4A-971B-6F1693738B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61827CCD-F915-1C4D-A974-AFAD095CBE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recipes" sheetId="1" r:id="rId1"/>

--- a/Recipe_Database_Corrected.xlsx
+++ b/Recipe_Database_Corrected.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taiyenwu/Downloads/Chef Tai/github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61827CCD-F915-1C4D-A974-AFAD095CBE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D522EF4B-10FA-324C-8D98-DD4EBB19CF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recipes" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="519">
   <si>
     <t>RecipeID</t>
   </si>
@@ -82,9 +82,6 @@
     <t>170C/340F</t>
   </si>
   <si>
-    <t>https://i.imgur.com/QXCoWk0.jpeg</t>
-  </si>
-  <si>
     <t>R002</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>180C/360F</t>
   </si>
   <si>
-    <t>https://i.imgur.com/nzrstcI.jpeg</t>
-  </si>
-  <si>
     <t>R003</t>
   </si>
   <si>
@@ -118,9 +112,6 @@
     <t>130C/275F</t>
   </si>
   <si>
-    <t>https://i.imgur.com/TIM3nkd.jpeg</t>
-  </si>
-  <si>
     <t>R004</t>
   </si>
   <si>
@@ -134,9 +125,6 @@
   </si>
   <si>
     <t>220C/430F</t>
-  </si>
-  <si>
-    <t>https://i.imgur.com/BqFfyM1.jpeg</t>
   </si>
   <si>
     <t>R005</t>
@@ -773,9 +761,6 @@
     <t>煎炒鍋</t>
   </si>
   <si>
-    <t>https://i.imgur.com/Zpxq8MV.jpeg</t>
-  </si>
-  <si>
     <t>將雞腿清洗乾淨後，撒上鹽、黑白胡椒、小蘇打粉與蒜末，拌勻醃製約 10 分鐘。</t>
   </si>
   <si>
@@ -804,9 +789,6 @@
   </si>
   <si>
     <t>Fry</t>
-  </si>
-  <si>
-    <t>https://i.imgur.com/TosqXXp.jpeg</t>
   </si>
   <si>
     <t>肉餡</t>
@@ -1065,9 +1047,6 @@
 Note: You can switch to top heat or broil during the last few minutes to slightly crisp the mashed potato surface.</t>
   </si>
   <si>
-    <t>https://i.imgur.com/CsbzD69.jpeg</t>
-  </si>
-  <si>
     <t>R008</t>
   </si>
   <si>
@@ -1171,9 +1150,6 @@
     <t>培根</t>
   </si>
   <si>
-    <t>https://i.imgur.com/nFDrjqe.jpeg</t>
-  </si>
-  <si>
     <t>R010</t>
   </si>
   <si>
@@ -1181,9 +1157,6 @@
   </si>
   <si>
     <t>台式海鮮粥</t>
-  </si>
-  <si>
-    <t>https://i.imgur.com/n66YFNB.jpeg</t>
   </si>
   <si>
     <t>Taiwaness-style</t>
@@ -1419,9 +1392,6 @@
     <t>Melting Butter</t>
   </si>
   <si>
-    <t>https://i.imgur.com/BtC3cL4.jpeg</t>
-  </si>
-  <si>
     <t>C018</t>
   </si>
   <si>
@@ -1540,9 +1510,6 @@
     <t>Mustard</t>
   </si>
   <si>
-    <t>https://i.imgur.com/3klYecs.jpeg</t>
-  </si>
-  <si>
     <t>熱狗麵包</t>
   </si>
   <si>
@@ -1616,6 +1583,42 @@
   </si>
   <si>
     <t>Grate some lemon zest over the filling, let it cool slightly, then freeze for a few hours before serving.</t>
+  </si>
+  <si>
+    <t>images/lemon_bar.jpg</t>
+  </si>
+  <si>
+    <t>images/scone.jpg</t>
+  </si>
+  <si>
+    <t>images/caramel_custard.jpg</t>
+  </si>
+  <si>
+    <t>images/strawberry_pei.jpg</t>
+  </si>
+  <si>
+    <t>images/korean_fried_chicken.jpg</t>
+  </si>
+  <si>
+    <t>images/pork_cheese_burger.jpg</t>
+  </si>
+  <si>
+    <t>images/shepherd_s_pie.jpg</t>
+  </si>
+  <si>
+    <t>images/pumpkin_soup.jpg</t>
+  </si>
+  <si>
+    <t>images/pumpkin_risotto.jpg</t>
+  </si>
+  <si>
+    <t>images/seafood_congee.jpg</t>
+  </si>
+  <si>
+    <t>images/cheery_pie.jpg</t>
+  </si>
+  <si>
+    <t>images/hot_dog_with_pepper_and_onion.jpg</t>
   </si>
 </sst>
 </file>
@@ -2103,16 +2106,16 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -2138,413 +2141,413 @@
         <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>507</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>508</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>509</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>510</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="L5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G6">
         <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>241</v>
+        <v>511</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>252</v>
+        <v>512</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="L7" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G8">
         <v>20</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>337</v>
+        <v>513</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D9" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E9" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G9">
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>371</v>
+        <v>514</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C10" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E10" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G10">
         <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>371</v>
+        <v>515</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B11" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D11" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E11" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>375</v>
+        <v>516</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B12" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C12" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D12" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12">
         <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>453</v>
+        <v>517</v>
       </c>
       <c r="I12" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="L12" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B13" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C13" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D13" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E13" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H13" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="I13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="L13" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="14:19" ht="18" x14ac:dyDescent="0.2">
@@ -2678,9 +2681,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H6" r:id="rId1" xr:uid="{C76906DE-C94F-294E-9842-D036BA878300}"/>
-    <hyperlink ref="H7" r:id="rId2" xr:uid="{9AADA651-C399-9541-8F39-30A11B5148B6}"/>
-    <hyperlink ref="H11" r:id="rId3" xr:uid="{3CABA0B3-95D4-E64C-B354-F6EE37A5A39C}"/>
+    <hyperlink ref="H6" r:id="rId1" xr:uid="{160EB18D-D101-8B4C-8399-F9B312811CF1}"/>
+    <hyperlink ref="H7" r:id="rId2" xr:uid="{2CD1C930-04CF-E94A-800F-1668089C852A}"/>
+    <hyperlink ref="H11" r:id="rId3" xr:uid="{F9B1354B-D738-8F49-BB78-25D334E4990F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2699,296 +2702,296 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3012,19 +3015,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -3032,16 +3035,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D2" s="5">
         <v>120</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F2" s="5" t="b">
         <v>0</v>
@@ -3052,16 +3055,16 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="5">
         <v>90</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F3" s="5" t="b">
         <v>0</v>
@@ -3072,16 +3075,16 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D4" s="5">
         <v>20</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F4" s="5" t="b">
         <v>0</v>
@@ -3092,16 +3095,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F5" s="5" t="b">
         <v>1</v>
@@ -3112,16 +3115,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D6" s="5">
         <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F6" s="5" t="b">
         <v>0</v>
@@ -3132,16 +3135,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5">
         <v>70</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F7" s="5" t="b">
         <v>0</v>
@@ -3152,16 +3155,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D8" s="5">
         <v>80</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F8" s="5" t="b">
         <v>0</v>
@@ -3172,16 +3175,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D9" s="5">
         <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F9" s="5" t="b">
         <v>0</v>
@@ -3192,16 +3195,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D10" s="5">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F10" s="5" t="b">
         <v>0</v>
@@ -3209,19 +3212,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D11" s="5">
         <v>210</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F11" s="5" t="b">
         <v>0</v>
@@ -3229,19 +3232,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D12" s="5">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F12" s="5" t="b">
         <v>0</v>
@@ -3249,19 +3252,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D13" s="5">
         <v>55</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F13" s="5" t="b">
         <v>0</v>
@@ -3269,19 +3272,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D14" s="5">
         <v>50</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F14" s="5" t="b">
         <v>0</v>
@@ -3289,19 +3292,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F15" s="5" t="b">
         <v>0</v>
@@ -3309,19 +3312,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D16" s="5">
         <v>85</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F16" s="5" t="b">
         <v>0</v>
@@ -3329,19 +3332,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" s="5">
         <v>0.5</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F17" s="5" t="b">
         <v>0</v>
@@ -3349,19 +3352,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F18" s="5" t="b">
         <v>0</v>
@@ -3369,19 +3372,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D19" s="5">
         <v>60</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F19" s="5" t="b">
         <v>0</v>
@@ -3389,19 +3392,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D20" s="5">
         <v>25</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F20" s="5" t="b">
         <v>0</v>
@@ -3409,19 +3412,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D21" s="5">
         <v>50</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F21" s="5" t="b">
         <v>0</v>
@@ -3429,19 +3432,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D22" s="5">
         <v>30</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F22" s="5" t="b">
         <v>0</v>
@@ -3449,19 +3452,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F23" s="5" t="b">
         <v>0</v>
@@ -3469,19 +3472,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D24" s="5">
         <v>200</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F24" s="5" t="b">
         <v>0</v>
@@ -3489,19 +3492,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D25" s="5">
         <v>140</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F25" s="5" t="b">
         <v>0</v>
@@ -3509,19 +3512,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D26" s="5">
         <v>4</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F26" s="5" t="b">
         <v>1</v>
@@ -3529,19 +3532,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D27" s="5">
         <v>2</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F27" s="5" t="b">
         <v>0</v>
@@ -3549,19 +3552,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F28" s="5" t="b">
         <v>0</v>
@@ -3569,19 +3572,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D29" s="5">
         <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F29" s="5" t="b">
         <v>1</v>
@@ -3589,19 +3592,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D30" s="5">
         <v>150</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F30" s="5" t="b">
         <v>0</v>
@@ -3609,19 +3612,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D31" s="5">
         <v>100</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F31" s="5" t="b">
         <v>0</v>
@@ -3629,19 +3632,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D32" s="5">
         <v>20</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F32" s="5" t="b">
         <v>0</v>
@@ -3649,19 +3652,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F33" s="5" t="b">
         <v>0</v>
@@ -3669,19 +3672,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D34" s="5">
         <v>60</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F34" s="5" t="b">
         <v>0</v>
@@ -3689,19 +3692,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D35" s="5">
         <v>1</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F35" s="5" t="b">
         <v>0</v>
@@ -3709,19 +3712,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D36" s="5">
         <v>6</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F36" s="5" t="b">
         <v>0</v>
@@ -3729,19 +3732,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D37" s="5">
         <v>30</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F37" s="5" t="b">
         <v>0</v>
@@ -3749,19 +3752,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D38" s="5">
         <v>0.5</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F38" s="5" t="b">
         <v>0</v>
@@ -3769,19 +3772,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D39" s="5">
         <v>200</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F39" s="5" t="b">
         <v>0</v>
@@ -3789,19 +3792,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D40" s="5">
         <v>40</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F40" s="5" t="b">
         <v>0</v>
@@ -3809,19 +3812,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D41" s="5">
         <v>4</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F41" s="5" t="b">
         <v>0</v>
@@ -3829,19 +3832,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D42" s="5">
         <v>1</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F42" s="5" t="b">
         <v>0</v>
@@ -3849,19 +3852,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D43" s="5">
         <v>10</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F43" s="5" t="b">
         <v>0</v>
@@ -3869,19 +3872,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F44" s="5" t="b">
         <v>0</v>
@@ -3889,19 +3892,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D45" s="5">
         <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F45" s="5" t="b">
         <v>0</v>
@@ -3909,19 +3912,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D46" s="5">
         <v>3</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F46" s="5" t="b">
         <v>0</v>
@@ -3929,19 +3932,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D47" s="5">
         <v>10</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F47" s="5" t="b">
         <v>0</v>
@@ -3949,19 +3952,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F48" s="5" t="b">
         <v>0</v>
@@ -3969,19 +3972,19 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D49" s="5">
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F49" s="5" t="b">
         <v>0</v>
@@ -3989,19 +3992,19 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D50" s="5">
         <v>2</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F50" s="5" t="b">
         <v>0</v>
@@ -4009,19 +4012,19 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D51" s="5">
         <v>1</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F51" s="5" t="b">
         <v>0</v>
@@ -4029,19 +4032,19 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D52" s="5">
         <v>5</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F52" s="5" t="b">
         <v>0</v>
@@ -4049,19 +4052,19 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D53" s="5">
         <v>4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F53" s="5" t="b">
         <v>0</v>
@@ -4069,19 +4072,19 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D54" s="5">
         <v>0.2</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F54" s="5" t="b">
         <v>0</v>
@@ -4093,19 +4096,19 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D55" s="5">
         <v>0.2</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F55" s="5" t="b">
         <v>0</v>
@@ -4117,19 +4120,19 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D56" s="5">
         <v>4</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F56" s="5" t="b">
         <v>0</v>
@@ -4141,19 +4144,19 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D57" s="5">
         <v>4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F57" s="5" t="b">
         <v>0</v>
@@ -4161,19 +4164,19 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D58" s="5">
         <v>3</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F58" s="5" t="b">
         <v>0</v>
@@ -4181,19 +4184,19 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D59" s="5">
         <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F59" s="5" t="b">
         <v>0</v>
@@ -4201,19 +4204,19 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D60" s="5">
         <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F60" s="5" t="b">
         <v>0</v>
@@ -4221,19 +4224,19 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D61" s="5">
         <v>1</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F61" s="5" t="b">
         <v>1</v>
@@ -4241,19 +4244,19 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D62" s="5">
         <v>1</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F62" s="5" t="b">
         <v>0</v>
@@ -4261,19 +4264,19 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D63" s="5">
         <v>2</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F63" s="5" t="b">
         <v>1</v>
@@ -4281,19 +4284,19 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D64" s="5">
         <v>400</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F64" s="5" t="b">
         <v>0</v>
@@ -4301,19 +4304,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D65" s="5">
         <v>0.5</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F65" s="5" t="b">
         <v>0</v>
@@ -4321,19 +4324,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F66" s="5" t="b">
         <v>0</v>
@@ -4341,19 +4344,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F67" s="5" t="b">
         <v>0</v>
@@ -4361,19 +4364,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D68" s="5">
         <v>1</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F68" s="5" t="b">
         <v>0</v>
@@ -4381,19 +4384,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D69" s="5">
         <v>1</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F69" s="5" t="b">
         <v>0</v>
@@ -4401,19 +4404,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D70" s="5">
         <v>200</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F70" s="5" t="b">
         <v>0</v>
@@ -4421,19 +4424,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D71" s="5">
         <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F71" s="5" t="b">
         <v>0</v>
@@ -4441,19 +4444,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>304</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>310</v>
       </c>
       <c r="D72" s="5">
         <v>0.5</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F72" s="5" t="b">
         <v>0</v>
@@ -4461,19 +4464,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D73" s="5">
         <v>0.5</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F73" s="5" t="b">
         <v>0</v>
@@ -4481,19 +4484,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>301</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>307</v>
       </c>
       <c r="D74" s="5">
         <v>3</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F74" s="5" t="b">
         <v>0</v>
@@ -4501,19 +4504,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D75" s="5">
         <v>1</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F75" s="5" t="b">
         <v>0</v>
@@ -4521,19 +4524,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D76" s="5">
         <v>0.5</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F76" s="5" t="b">
         <v>0</v>
@@ -4541,19 +4544,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D77" s="5">
         <v>30</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F77" s="5" t="b">
         <v>0</v>
@@ -4561,19 +4564,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F78" s="5" t="b">
         <v>1</v>
@@ -4581,19 +4584,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D79" s="5">
         <v>1</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F79" s="5" t="b">
         <v>0</v>
@@ -4601,19 +4604,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D80" s="5">
         <v>1</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F80" s="5" t="b">
         <v>0</v>
@@ -4621,19 +4624,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D81" s="5">
         <v>1</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F81" s="5" t="b">
         <v>0</v>
@@ -4641,19 +4644,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F82" s="5" t="b">
         <v>0</v>
@@ -4661,19 +4664,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D83" s="5">
         <v>1</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F83" s="5" t="b">
         <v>0</v>
@@ -4681,19 +4684,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D84" s="5">
         <v>0.5</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F84" s="5" t="b">
         <v>0</v>
@@ -4701,19 +4704,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D85" s="5">
         <v>1</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F85" s="5" t="b">
         <v>0</v>
@@ -4721,19 +4724,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D86" s="5">
         <v>0.5</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F86" s="5" t="b">
         <v>0</v>
@@ -4741,19 +4744,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>345</v>
-      </c>
       <c r="D87" s="5">
         <v>1</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F87" s="5" t="b">
         <v>0</v>
@@ -4761,19 +4764,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B88" s="5" t="s">
-        <v>367</v>
-      </c>
       <c r="C88" s="5" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D88" s="5">
         <v>0.5</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F88" s="5" t="b">
         <v>0</v>
@@ -4781,19 +4784,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>367</v>
-      </c>
       <c r="C89" s="5" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D89" s="5">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F89" s="5" t="b">
         <v>0</v>
@@ -4801,19 +4804,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B90" s="5" t="s">
-        <v>367</v>
-      </c>
       <c r="C90" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D90" s="5">
         <v>0.5</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F90" s="5" t="b">
         <v>0</v>
@@ -4821,19 +4824,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>367</v>
-      </c>
       <c r="C91" s="5" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="D91" s="5">
         <v>1</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F91" s="5" t="b">
         <v>0</v>
@@ -4841,19 +4844,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="D92" s="5">
         <v>4</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F92" s="5" t="b">
         <v>0</v>
@@ -4861,19 +4864,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D93" s="5">
         <v>0.5</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F93" s="5" t="b">
         <v>0</v>
@@ -4881,19 +4884,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D94" s="5">
         <v>1</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F94" s="5" t="b">
         <v>0</v>
@@ -4901,19 +4904,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D95" s="5">
         <v>5</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F95" s="5" t="b">
         <v>0</v>
@@ -4921,19 +4924,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D96" s="5">
         <v>10</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F96" s="5" t="b">
         <v>0</v>
@@ -4941,19 +4944,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D97" s="5">
         <v>2</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F97" s="5" t="b">
         <v>0</v>
@@ -4961,19 +4964,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D98" s="5">
         <v>2</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F98" s="5" t="b">
         <v>0</v>
@@ -4981,19 +4984,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F99" s="5" t="b">
         <v>0</v>
@@ -5001,19 +5004,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D100" s="5">
         <v>1</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F100" s="5" t="b">
         <v>0</v>
@@ -5021,19 +5024,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D101" s="5">
         <v>1</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F101" s="5" t="b">
         <v>0</v>
@@ -5041,19 +5044,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D102" s="5">
         <v>1</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F102" s="5" t="b">
         <v>0</v>
@@ -5061,19 +5064,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="D103" s="5">
         <v>80</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F103" s="5" t="b">
         <v>0</v>
@@ -5081,19 +5084,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="D104" s="5">
         <v>2</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F104" s="5" t="b">
         <v>0</v>
@@ -5101,19 +5104,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D105" s="5">
         <v>0.25</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F105" s="5" t="b">
         <v>0</v>
@@ -5121,19 +5124,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D106" s="5">
         <v>1</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F106" s="5" t="b">
         <v>0</v>
@@ -5141,19 +5144,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F107" s="5" t="b">
         <v>0</v>
@@ -5161,19 +5164,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D108" s="5">
         <v>1</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F108" s="5" t="b">
         <v>0</v>
@@ -5181,19 +5184,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D109" s="5">
         <v>5</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F109" s="5" t="b">
         <v>1</v>
@@ -5201,19 +5204,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D110" s="5">
         <v>4</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F110" s="5" t="b">
         <v>0</v>
@@ -5221,19 +5224,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D111" s="5">
         <v>1</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F111" s="5" t="b">
         <v>1</v>
@@ -5241,19 +5244,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D112" s="5">
         <v>6</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F112" s="5" t="b">
         <v>0</v>
@@ -5261,19 +5264,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D113" s="5">
         <v>6</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F113" s="5" t="b">
         <v>1</v>
@@ -5281,19 +5284,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D114" s="5">
         <v>1</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F114" s="5" t="b">
         <v>0</v>
@@ -5301,19 +5304,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D115" s="5">
         <v>1</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F115" s="5" t="b">
         <v>0</v>
@@ -5321,19 +5324,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D116" s="5">
         <v>40</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F116" s="5" t="b">
         <v>0</v>
@@ -5341,19 +5344,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="D117" s="5">
         <v>60</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F117" s="5" t="b">
         <v>0</v>
@@ -5361,19 +5364,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D118" s="5">
         <v>100</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F118" s="5" t="b">
         <v>0</v>
@@ -5381,19 +5384,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>446</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>456</v>
       </c>
       <c r="D119" s="5">
         <v>10</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F119" s="5" t="b">
         <v>1</v>
@@ -5401,19 +5404,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D120" s="5">
         <v>1</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F120" s="5" t="b">
         <v>0</v>
@@ -5421,19 +5424,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D121" s="5">
         <v>10</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F121" s="5" t="b">
         <v>0</v>
@@ -5441,19 +5444,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D122" s="5">
         <v>4</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F122" s="5" t="b">
         <v>0</v>
@@ -5461,19 +5464,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D123" s="5">
         <v>24</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F123" s="5" t="b">
         <v>0</v>
@@ -5481,19 +5484,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D124" s="5">
         <v>40</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F124" s="5" t="b">
         <v>0</v>
@@ -5501,19 +5504,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D125" s="5">
         <v>1</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F125" s="5" t="b">
         <v>0</v>
@@ -5521,19 +5524,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C126" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="D126" s="5">
         <v>2</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F126" s="5" t="b">
         <v>0</v>
@@ -5541,19 +5544,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C127" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D127" s="5">
         <v>2</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F127" s="5" t="b">
         <v>0</v>
@@ -5561,19 +5564,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C128" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="D128" s="5">
         <v>0.25</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F128" s="5" t="b">
         <v>0</v>
@@ -5581,19 +5584,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C129" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="D129" s="5">
         <v>0.25</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F129" s="5" t="b">
         <v>0</v>
@@ -5601,19 +5604,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C130" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D130" s="5">
         <v>0.25</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F130" s="5" t="b">
         <v>0</v>
@@ -5621,19 +5624,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C131" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D131" s="5">
         <v>2</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F131" s="5" t="b">
         <v>1</v>
@@ -5641,19 +5644,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C132" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D132" s="5">
         <v>1</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F132" s="5" t="b">
         <v>0</v>
@@ -5661,19 +5664,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C133" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D133" s="5">
         <v>1</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F133" s="5" t="b">
         <v>0</v>
@@ -5681,19 +5684,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C134" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="D134" s="5">
         <v>1</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F134" s="5" t="b">
         <v>0</v>
@@ -5701,19 +5704,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D135" s="5">
         <v>1</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F135" s="5" t="b">
         <v>0</v>
@@ -5731,146 +5734,146 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -5883,130 +5886,130 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B22" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
         <v>16</v>
-      </c>
-      <c r="B24" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -6015,10 +6018,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -6027,10 +6030,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B37" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -6039,58 +6042,58 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B39" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B42" t="s">
         <v>305</v>
-      </c>
-      <c r="B42" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B43" t="s">
         <v>306</v>
-      </c>
-      <c r="B43" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B44" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -6099,40 +6102,40 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B45" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="G48" s="2"/>
       <c r="I48" s="4"/>
@@ -6140,236 +6143,236 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B56" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B61" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B62" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B64" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B65" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B66" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B67" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="B68" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B69" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="B73" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B75" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -6400,25 +6403,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6429,16 +6432,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G2" s="4">
         <v>2</v>
@@ -6455,16 +6458,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="G3" s="4">
         <v>5</v>
@@ -6481,16 +6484,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G4" s="4">
         <v>2</v>
@@ -6507,16 +6510,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G5" s="4">
         <v>22</v>
@@ -6533,16 +6536,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="G6" s="4">
         <v>5</v>
@@ -6559,16 +6562,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
@@ -6585,16 +6588,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="G8" s="4">
         <v>10</v>
@@ -6611,16 +6614,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -6631,22 +6634,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G10" s="4">
         <v>3</v>
@@ -6657,22 +6660,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G11" s="4">
         <v>5</v>
@@ -6683,22 +6686,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <v>3</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G12" s="4">
         <v>2</v>
@@ -6709,22 +6712,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G13" s="4">
         <v>5</v>
@@ -6735,22 +6738,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <v>5</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G14" s="4">
         <v>3</v>
@@ -6761,22 +6764,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4">
         <v>6</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G15" s="4">
         <v>2</v>
@@ -6787,22 +6790,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4">
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G16" s="4">
         <v>1</v>
@@ -6813,22 +6816,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="4">
         <v>8</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G17" s="4">
         <v>20</v>
@@ -6839,22 +6842,22 @@
     </row>
     <row r="18" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G18" s="4">
         <v>5</v>
@@ -6865,22 +6868,22 @@
     </row>
     <row r="19" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <v>2</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G19" s="4">
         <v>3</v>
@@ -6891,22 +6894,22 @@
     </row>
     <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4">
         <v>3</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G20" s="4">
         <v>10</v>
@@ -6917,22 +6920,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4">
         <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G21" s="4">
         <v>1</v>
@@ -6943,22 +6946,22 @@
     </row>
     <row r="22" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4">
         <v>5</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G22" s="4">
         <v>3</v>
@@ -6969,22 +6972,22 @@
     </row>
     <row r="23" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="4">
         <v>6</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G23" s="4">
         <v>1</v>
@@ -6995,22 +6998,22 @@
     </row>
     <row r="24" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="4">
         <v>7</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G24" s="4">
         <v>1</v>
@@ -7026,22 +7029,22 @@
     </row>
     <row r="25" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25" s="4">
         <v>8</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F25" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G25" s="4">
         <v>5</v>
@@ -7052,22 +7055,22 @@
     </row>
     <row r="26" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B26" s="4">
         <v>9</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G26" s="4">
         <v>3</v>
@@ -7078,22 +7081,22 @@
     </row>
     <row r="27" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="4">
         <v>10</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
@@ -7104,22 +7107,22 @@
     </row>
     <row r="28" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B28" s="4">
         <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G28" s="4">
         <v>65</v>
@@ -7130,22 +7133,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B29" s="4">
         <v>12</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G29" s="4">
         <v>0</v>
@@ -7156,22 +7159,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B30" s="4">
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
@@ -7182,22 +7185,22 @@
     </row>
     <row r="31" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B31" s="4">
         <v>2</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G31" s="4">
         <v>3</v>
@@ -7208,22 +7211,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B32" s="4">
         <v>3</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G32" s="4">
         <v>60</v>
@@ -7234,22 +7237,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B33" s="4">
         <v>4</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E33" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F33" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G33" s="4">
         <v>5</v>
@@ -7260,22 +7263,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B34" s="4">
         <v>5</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E34" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F34" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G34" s="4">
         <v>3</v>
@@ -7286,22 +7289,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B35" s="4">
         <v>6</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F35" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G35" s="4">
         <v>3</v>
@@ -7312,22 +7315,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B36" s="4">
         <v>7</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F36" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G36" s="4">
         <v>5</v>
@@ -7338,22 +7341,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B37" s="4">
         <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F37" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G37" s="4">
         <v>2</v>
@@ -7364,22 +7367,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B38" s="4">
         <v>9</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E38" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F38" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G38" s="4">
         <v>25</v>
@@ -7390,22 +7393,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B39" s="4">
         <v>1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F39" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G39" s="4">
         <v>10</v>
@@ -7416,22 +7419,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B40" s="4">
         <v>2</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="F40" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="G40" s="4">
         <v>50</v>
@@ -7442,22 +7445,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B41" s="4">
         <v>3</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F41" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G41" s="4">
         <v>5</v>
@@ -7468,22 +7471,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B42" s="4">
         <v>4</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="F42" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G42" s="9">
         <v>5</v>
@@ -7494,22 +7497,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B43" s="4">
         <v>5</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F43" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G43" s="9">
         <v>1</v>
@@ -7520,22 +7523,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B44" s="4">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>253</v>
-      </c>
       <c r="E44" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F44" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G44" s="9">
         <v>5</v>
@@ -7546,22 +7549,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B45" s="4">
         <v>2</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E45" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F45" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G45" s="9">
         <v>5</v>
@@ -7572,22 +7575,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E46" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="F46" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G46" s="9">
         <v>3</v>
@@ -7598,22 +7601,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B47" s="4">
         <v>4</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F47" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G47" s="9">
         <v>2</v>
@@ -7624,22 +7627,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B48" s="4">
         <v>5</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="F48" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G48" s="9">
         <v>3</v>
@@ -7650,22 +7653,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B49" s="4">
         <v>6</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F49" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G49" s="9">
         <v>5</v>
@@ -7676,22 +7679,22 @@
     </row>
     <row r="50" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B50" s="4">
         <v>7</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="G50" s="9">
         <v>10</v>
@@ -7702,22 +7705,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B51" s="4">
         <v>8</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F51" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G51" s="9">
         <v>5</v>
@@ -7728,22 +7731,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F52" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G52" s="9">
         <v>10</v>
@@ -7754,22 +7757,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B53" s="4">
         <v>2</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F53" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="G53" s="9">
         <v>10</v>
@@ -7780,22 +7783,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B54" s="4">
         <v>3</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="F54" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="G54" s="9">
         <v>5</v>
@@ -7806,22 +7809,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B55" s="4">
         <v>4</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F55" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="G55" s="9">
         <v>10</v>
@@ -7832,22 +7835,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B56" s="4">
         <v>5</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F56" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G56" s="9">
         <v>5</v>
@@ -7858,22 +7861,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B57" s="4">
         <v>6</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F57" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="G57" s="9">
         <v>1</v>
@@ -7884,22 +7887,22 @@
     </row>
     <row r="58" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B58" s="4">
         <v>7</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="G58" s="9">
         <v>20</v>
@@ -7910,22 +7913,22 @@
     </row>
     <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B59" s="4">
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G59" s="9">
         <v>10</v>
@@ -7936,22 +7939,22 @@
     </row>
     <row r="60" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B60" s="4">
         <v>2</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G60" s="9">
         <v>1</v>
@@ -7962,22 +7965,22 @@
     </row>
     <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B61" s="4">
         <v>3</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="G61" s="9">
         <v>20</v>
@@ -7988,22 +7991,22 @@
     </row>
     <row r="62" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B62" s="4">
         <v>4</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G62" s="9">
         <v>1</v>
@@ -8014,22 +8017,22 @@
     </row>
     <row r="63" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B63" s="4">
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="G63" s="9">
         <v>32</v>
@@ -8040,22 +8043,22 @@
     </row>
     <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B64" s="4">
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E64" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="G64" s="9">
         <v>10</v>
@@ -8066,22 +8069,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B65" s="4">
         <v>2</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E65" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="F65" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="G65" s="9">
         <v>5</v>
@@ -8092,22 +8095,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B66" s="4">
         <v>3</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E66" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F66" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="G66" s="9">
         <v>3</v>
@@ -8118,22 +8121,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B67" s="4">
         <v>4</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E67" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="F67" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="G67" s="9">
         <v>3</v>
@@ -8144,22 +8147,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B68" s="4">
         <v>5</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E68" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F68" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="G68" s="9">
         <v>3</v>
@@ -8170,22 +8173,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B69" s="4">
         <v>6</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E69" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="F69" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="G69" s="4">
         <v>1</v>
@@ -8196,22 +8199,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B70" s="4">
         <v>7</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E70" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="F70" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="G70" s="4">
         <v>20</v>
@@ -8222,22 +8225,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B71" s="4">
         <v>8</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E71" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F71" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -8248,22 +8251,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B72" s="4">
         <v>9</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E72" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F72" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="G72" s="4">
         <v>0</v>
@@ -8274,22 +8277,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B73" s="4">
         <v>10</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E73" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="F73" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="G73" s="4">
         <v>1</v>
@@ -8300,22 +8303,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B74" s="4">
         <v>1</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E74" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="F74" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G74" s="9">
         <v>50</v>
@@ -8326,22 +8329,22 @@
     </row>
     <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B75" s="4">
         <v>2</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F75" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="G75" s="9">
         <v>10</v>
@@ -8352,22 +8355,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B76" s="4">
         <v>3</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E76" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="F76" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="G76" s="9">
         <v>10</v>
@@ -8378,22 +8381,22 @@
     </row>
     <row r="77" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B77" s="4">
         <v>4</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F77" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="G77" s="9">
         <v>10</v>
@@ -8404,22 +8407,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B78" s="4">
         <v>5</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F78" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="G78" s="9">
         <v>10</v>
@@ -8430,22 +8433,22 @@
     </row>
     <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B79" s="4">
         <v>6</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F79" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="G79" s="9">
         <v>1</v>
@@ -8456,22 +8459,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B80" s="4">
         <v>7</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E80" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="F80" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="G80" s="9">
         <v>1</v>
@@ -8482,22 +8485,22 @@
     </row>
     <row r="81" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B81" s="4">
         <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="G81" s="9">
         <v>5</v>
@@ -8508,22 +8511,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B82" s="4">
         <v>2</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E82" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="F82" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="G82" s="9">
         <v>30</v>
@@ -8534,22 +8537,22 @@
     </row>
     <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B83" s="4">
         <v>3</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="F83" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="G83" s="9">
         <v>1</v>
@@ -8560,22 +8563,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B84" s="4">
         <v>4</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E84" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F84" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="G84" s="9">
         <v>5</v>
@@ -8586,22 +8589,22 @@
     </row>
     <row r="85" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B85" s="4">
         <v>5</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="F85" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="G85" s="9">
         <v>1</v>
@@ -8612,22 +8615,22 @@
     </row>
     <row r="86" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B86" s="4">
         <v>6</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="G86" s="9">
         <v>3</v>
@@ -8638,22 +8641,22 @@
     </row>
     <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B87" s="4">
         <v>7</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F87" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G87" s="9">
         <v>40</v>
@@ -8664,22 +8667,22 @@
     </row>
     <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B88" s="4">
         <v>8</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="F88" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="G88" s="9">
         <v>0</v>
@@ -8690,22 +8693,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B89" s="4">
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E89" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="F89" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="G89" s="9">
         <v>3</v>
@@ -8716,22 +8719,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B90" s="4">
         <v>2</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E90" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="F90" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="G90" s="9">
         <v>5</v>
@@ -8742,22 +8745,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B91" s="4">
         <v>3</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E91" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="F91" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="G91" s="9">
         <v>1</v>
@@ -8768,22 +8771,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B92" s="4">
         <v>4</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E92" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="F92" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="G92" s="4">
         <v>3</v>
@@ -8794,22 +8797,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B93" s="4">
         <v>5</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E93" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="F93" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="G93" s="4">
         <v>5</v>
@@ -8820,22 +8823,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B94" s="4">
         <v>6</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E94" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="F94" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="G94" s="9">
         <v>3</v>
@@ -8869,13 +8872,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -8883,10 +8886,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -8897,10 +8900,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -8911,10 +8914,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -8925,10 +8928,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -8939,10 +8942,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -8953,10 +8956,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -8967,10 +8970,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -8981,10 +8984,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -8992,13 +8995,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -9006,13 +9009,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -9020,13 +9023,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -9034,13 +9037,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -9048,13 +9051,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -9062,13 +9065,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -9076,13 +9079,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -9090,13 +9093,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C17" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -9104,13 +9107,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C18" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -9118,13 +9121,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -9132,13 +9135,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -9146,13 +9149,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -9160,13 +9163,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C22" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -9174,13 +9177,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -9188,13 +9191,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -9202,13 +9205,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -9216,13 +9219,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -9230,13 +9233,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -9244,13 +9247,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -9258,13 +9261,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -9272,13 +9275,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C30" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -9286,13 +9289,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C31" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -9300,13 +9303,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
@@ -9314,13 +9317,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
@@ -9328,13 +9331,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D34" t="b">
         <v>0</v>
@@ -9342,13 +9345,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D35" t="b">
         <v>0</v>
@@ -9356,13 +9359,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C36" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D36" t="b">
         <v>0</v>
@@ -9370,13 +9373,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D37" t="b">
         <v>0</v>
@@ -9384,13 +9387,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C38" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D38" t="b">
         <v>0</v>
@@ -9398,13 +9401,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C39" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
@@ -9412,13 +9415,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C40" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D40" t="b">
         <v>0</v>
@@ -9426,13 +9429,13 @@
     </row>
     <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C41" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D41" t="b">
         <v>0</v>
@@ -9441,13 +9444,13 @@
     </row>
     <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D42" t="b">
         <v>0</v>
@@ -9456,13 +9459,13 @@
     </row>
     <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B43" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C43" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D43" t="b">
         <v>0</v>
@@ -9471,13 +9474,13 @@
     </row>
     <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B44" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D44" t="b">
         <v>0</v>
@@ -9486,13 +9489,13 @@
     </row>
     <row r="45" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C45" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="D45" t="b">
         <v>1</v>
@@ -9501,13 +9504,13 @@
     </row>
     <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D46" t="b">
         <v>0</v>
@@ -9516,13 +9519,13 @@
     </row>
     <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B47" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C47" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D47" t="b">
         <v>0</v>
@@ -9531,13 +9534,13 @@
     </row>
     <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D48" t="b">
         <v>0</v>

--- a/Recipe_Database_Corrected.xlsx
+++ b/Recipe_Database_Corrected.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taiyenwu/Downloads/Chef Tai/github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D522EF4B-10FA-324C-8D98-DD4EBB19CF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC81B37-CE20-A045-8E18-21F9E80534A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2067,7 +2067,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.33203125" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>

--- a/Recipe_Database_Corrected.xlsx
+++ b/Recipe_Database_Corrected.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taiyenwu/Downloads/Chef Tai/github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61827CCD-F915-1C4D-A974-AFAD095CBE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272DE809-DD32-6D4F-909A-2824696532BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="5920" windowWidth="38560" windowHeight="19060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26660" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recipes" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="456">
   <si>
     <t>RecipeID</t>
   </si>
@@ -490,6 +490,18 @@
     <t>將烤模放入烤箱，以170°C烘烤約22分鐘。</t>
   </si>
   <si>
+    <t>將奶油、檸檬汁、糖和雞蛋混合攪拌均勻，表面的氣泡可用餐巾紙吸附去除。</t>
+  </si>
+  <si>
+    <t>將攪拌好的餡料倒入烤好的餅皮模具中。</t>
+  </si>
+  <si>
+    <t>將模具再次放入烤箱，以170°C烘烤約10分鐘。</t>
+  </si>
+  <si>
+    <t>烤好後，刨上檸檬屑，並用喜歡的水果裝飾。</t>
+  </si>
+  <si>
     <t>Grease the baking mold with butter and line it with parchment paper.</t>
   </si>
   <si>
@@ -497,6 +509,18 @@
   </si>
   <si>
     <t>Bake in the oven at 170°C (340°F) for about 22 minutes.</t>
+  </si>
+  <si>
+    <t>Mix butter, lemon juice, sugar, and eggs until well combined. Remove any surface bubbles by dabbing with a paper towel.</t>
+  </si>
+  <si>
+    <t>Pour the filling into the baked crust in the mold.</t>
+  </si>
+  <si>
+    <t>Bake again in the oven at 170°C (340°F) for about 10 minutes.</t>
+  </si>
+  <si>
+    <t>After baking, sprinkle with lemon zest and decorate with your favorite fruits.</t>
   </si>
   <si>
     <t>CycleTime</t>
@@ -779,6 +803,9 @@
     <t>將雞腿清洗乾淨後，撒上鹽、黑白胡椒、小蘇打粉與蒜末，拌勻醃製約 10 分鐘。</t>
   </si>
   <si>
+    <t>將雞腿放入烤箱，以 200°C / 400°F 烘烤約 50 分鐘，至表皮微酥金黃。</t>
+  </si>
+  <si>
     <t>將番茄醬、糖、蜂蜜與韓式辣醬依比例放入平底鍋中，加入適量清水攪拌均勻。</t>
   </si>
   <si>
@@ -949,6 +976,9 @@
     <t>Rinse the chicken dBrandysticks thoroughly, then season with salt, black and white pepper, baking soda, and minced garlic. Mix well and marinate for about 10 minutes.</t>
   </si>
   <si>
+    <t>Place the dBrandysticks in an oven preheated to 200°C / 400°F and roast for approximately 50 minutes, until the skin turns golden and slightly crispy.</t>
+  </si>
+  <si>
     <t>Add the roasted dBrandysticks to the skillet, coating them evenly with the sauce. Simmer over low heat until the sauce thickens and clings to the chicken.</t>
   </si>
   <si>
@@ -1396,233 +1426,13 @@
   <si>
     <t>Prepare the pumpkin sauce based on a pumpkin soup recipe.
 Note: Since this sauce will be used as a cooking sauce, it’s recommended to reduce the amount of water from the original recipe to achieve a thicker consistency.</t>
-  </si>
-  <si>
-    <t>R011</t>
-  </si>
-  <si>
-    <t>Cheery Pie</t>
-  </si>
-  <si>
-    <t>櫻桃派</t>
-  </si>
-  <si>
-    <t>4 Serves</t>
-  </si>
-  <si>
-    <t>Cherry</t>
-  </si>
-  <si>
-    <t>Almind flour</t>
-  </si>
-  <si>
-    <t>Melting Butter</t>
-  </si>
-  <si>
-    <t>https://i.imgur.com/BtC3cL4.jpeg</t>
-  </si>
-  <si>
-    <t>C018</t>
-  </si>
-  <si>
-    <t>C019</t>
-  </si>
-  <si>
-    <t>Vanilla extract</t>
-  </si>
-  <si>
-    <t>香草精</t>
-  </si>
-  <si>
-    <t>融化奶油</t>
-  </si>
-  <si>
-    <t>櫻桃</t>
-  </si>
-  <si>
-    <t>Pie Dish</t>
-  </si>
-  <si>
-    <t>派模</t>
-  </si>
-  <si>
-    <t>去核器</t>
-  </si>
-  <si>
-    <t>Pitter</t>
-  </si>
-  <si>
-    <t>將櫻桃洗淨擦乾後，去核置入碗中。
-筆記：若無去核器，可使用金屬吸管代替。</t>
-  </si>
-  <si>
-    <t>加入糖粉與檸檬汁，混合均勻後，放入冰箱醃製至少 30 分鐘。</t>
-  </si>
-  <si>
-    <t>在派模內部塗上一層奶油，撒上些許砂糖，搖晃使糖粒均勻附著。</t>
-  </si>
-  <si>
-    <t>打入雞蛋，加入一小撮鹽，接著過篩麵粉、杏仁粉與糖粉後倒入，一起攪拌均勻。</t>
-  </si>
-  <si>
-    <t>加入牛奶、香草精與融化奶油，再次拌勻成滑順麵糊。</t>
-  </si>
-  <si>
-    <t>將醃製好的櫻桃倒入派模中，再倒入麵糊。
-筆記：麵糊加入至櫻桃稍微浮起即可。</t>
-  </si>
-  <si>
-    <t>放入預熱至 180°C 的烤箱，烘烤約 40 分鐘，表面上色且中心熟透即可。放涼後即可享用。置入烤箱 180度c 烤40分鐘左右出爐，放涼即可享用</t>
-  </si>
-  <si>
-    <t>食用前可撒上糖粉，增加風味與美感。</t>
-  </si>
-  <si>
-    <t>Wash and dry the cherries thoroughly, then pit them and place into a bowl.
-Note: If you don't have a cherry pitter, a metal straw works well as an alternative.</t>
-  </si>
-  <si>
-    <t>Add powdered sugar and lemon juice. Mix well, then refrigerate for at least 30 minutes.</t>
-  </si>
-  <si>
-    <t>Grease the inside of the pie dish with butter, then sprinkle a little granulated sugar. Shake gently to coat evenly.</t>
-  </si>
-  <si>
-    <t>Crack the eggs into a bowl and add a small pinch of salt. Sift in the flour, almond flour, and powdered sugar. Mix until smooth.</t>
-  </si>
-  <si>
-    <t>Add milk, vanilla extract, and melted butter, and stir until fully combined and smooth.</t>
-  </si>
-  <si>
-    <t>Spread the marinated cherries evenly in the pie dish, then pour in the batter.
-Note: Pour just enough batter so the cherries begin to slightly float.</t>
-  </si>
-  <si>
-    <t>Bake in a preheated oven at 180°C (360°F) for about 40 minutes, or until golden and set in the center. Let cool before serving.</t>
-  </si>
-  <si>
-    <t>Dust with powdered sugar before serving for extra flavor and a beautiful finish.</t>
-  </si>
-  <si>
-    <t>杏仁麵粉</t>
-  </si>
-  <si>
-    <t>將雞腿放入烤箱，以 200°C / 400°F 烘烤約 35 分鐘，至表皮微酥金黃。</t>
-  </si>
-  <si>
-    <t>Place the dBrandysticks in an oven preheated to 200°C / 400°F and roast for approximately 35 minutes, until the skin turns golden and slightly crispy.</t>
-  </si>
-  <si>
-    <t>R012</t>
-  </si>
-  <si>
-    <t>Hot dog with Pepper and Onion</t>
-  </si>
-  <si>
-    <t>椒香熱狗堡</t>
-  </si>
-  <si>
-    <t>C020</t>
-  </si>
-  <si>
-    <t>Hot dog bun</t>
-  </si>
-  <si>
-    <t>Hot dog</t>
-  </si>
-  <si>
-    <t>Green Pepper</t>
-  </si>
-  <si>
-    <t>Red Pepper</t>
-  </si>
-  <si>
-    <t>Mustard</t>
-  </si>
-  <si>
-    <t>https://i.imgur.com/3klYecs.jpeg</t>
-  </si>
-  <si>
-    <t>熱狗麵包</t>
-  </si>
-  <si>
-    <t>青椒</t>
-  </si>
-  <si>
-    <t>紅椒</t>
-  </si>
-  <si>
-    <t>芥末醬</t>
-  </si>
-  <si>
-    <t>熱狗</t>
-  </si>
-  <si>
-    <t>將洋蔥、紅椒、青椒洗淨後切成細絲。</t>
-  </si>
-  <si>
-    <t>熱鍋加油，先下洋蔥炒至金黃，再加入紅椒與青椒翻炒至熟。</t>
-  </si>
-  <si>
-    <t>倒入少量白蘭地嗆鍋提味，接著加入鹽與黑胡椒調味。喜歡微辣口感的話，也可加入幾滴 Tabasco。炒好後起鍋備用。</t>
-  </si>
-  <si>
-    <t>將熱狗麵包放入烤箱加熱。</t>
-  </si>
-  <si>
-    <t>另起一鍋，將熱狗煎至表面微焦、熟透。</t>
-  </si>
-  <si>
-    <t>組裝時，將煎好的熱狗夾入麵包中，再鋪上炒好的洋蔥與椒絲。最後依個人口味加入番茄醬與芥末醬即可享用。</t>
-  </si>
-  <si>
-    <t>Wash the onion, red bell pepper, and green bell pepper. Slice them into thin strips.</t>
-  </si>
-  <si>
-    <t>Heat a pan with oil. Sauté the onions until golden, then add the red and green peppers. Stir-fry until cooked through.</t>
-  </si>
-  <si>
-    <t>Add a splash of brandy to deglaze the pan and enhance the flavor. Season with salt and black pepper. For a spicy kick, add a few drops of Tabasco. Set the mixture aside.</t>
-  </si>
-  <si>
-    <t>Warm the hot dog buns in the oven.</t>
-  </si>
-  <si>
-    <t>In a separate pan, pan-fry the hot dogs until nicely browned and fully cooked.</t>
-  </si>
-  <si>
-    <t>To assemble, place the hot dog into the bun, top with the sautéed onions and peppers, then add ketchup and mustard to taste. Enjoy!</t>
-  </si>
-  <si>
-    <t>將檸檬汁、糖、蛋黃和全蛋混合，攪拌均勻。</t>
-  </si>
-  <si>
-    <t>隔水加熱方式烹煮，將溫度控制在約 80°C（176°F），注意不要煮滾。</t>
-  </si>
-  <si>
-    <t>將奶油加入並攪拌至完全融合，然後將餡料倒入已烤好的餅皮模具中。</t>
-  </si>
-  <si>
-    <t>用刨絲器刨一些檸檬皮，稍微降溫後，放入冷凍數小時即可食用。</t>
-  </si>
-  <si>
-    <t>Combine lemon juice, sugar, egg yolks, and whole eggs, and mix until smooth.</t>
-  </si>
-  <si>
-    <t>Add butter and stir until fully incorporated, then pour the filling into the pre-baked tart shells.</t>
-  </si>
-  <si>
-    <t>Cook over a double boiler, keeping the temperature around 80°C (175°F), being careful not to let it boil.</t>
-  </si>
-  <si>
-    <t>Grate some lemon zest over the filling, let it cool slightly, then freeze for a few hours before serving.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1657,25 +1467,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1725,7 +1516,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1750,13 +1541,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2060,21 +1844,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -2290,7 +2068,7 @@
         <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>128</v>
@@ -2307,22 +2085,22 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>128</v>
@@ -2339,16 +2117,16 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -2360,7 +2138,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>128</v>
@@ -2377,31 +2155,31 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B9" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D9" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="E9" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G9">
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>131</v>
@@ -2412,25 +2190,25 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C10" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="D10" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="E10" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G10">
         <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>128</v>
@@ -2447,22 +2225,22 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B11" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D11" t="s">
         <v>373</v>
       </c>
-      <c r="C11" t="s">
-        <v>374</v>
-      </c>
-      <c r="D11" t="s">
-        <v>363</v>
-      </c>
       <c r="E11" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>128</v>
@@ -2471,210 +2249,11 @@
         <v>140</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>446</v>
-      </c>
-      <c r="B12" t="s">
-        <v>447</v>
-      </c>
-      <c r="C12" t="s">
-        <v>448</v>
-      </c>
-      <c r="D12" t="s">
-        <v>449</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12">
-        <v>40</v>
-      </c>
-      <c r="H12" t="s">
-        <v>453</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>483</v>
-      </c>
-      <c r="B13" t="s">
-        <v>484</v>
-      </c>
-      <c r="C13" t="s">
-        <v>485</v>
-      </c>
-      <c r="D13" t="s">
-        <v>363</v>
-      </c>
-      <c r="E13" t="s">
-        <v>251</v>
-      </c>
-      <c r="H13" t="s">
-        <v>492</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="14:19" ht="18" x14ac:dyDescent="0.2">
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-    </row>
-    <row r="27" spans="14:19" ht="18" x14ac:dyDescent="0.2">
-      <c r="N27" s="11"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
-    </row>
-    <row r="28" spans="14:19" ht="18" x14ac:dyDescent="0.2">
-      <c r="N28" s="11"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-    </row>
-    <row r="29" spans="14:19" ht="18" x14ac:dyDescent="0.2">
-      <c r="N29" s="11"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-    </row>
-    <row r="30" spans="14:19" ht="18" x14ac:dyDescent="0.2">
-      <c r="O30" s="12"/>
-      <c r="R30" s="11"/>
-    </row>
-    <row r="31" spans="14:19" ht="18" x14ac:dyDescent="0.2">
-      <c r="N31" s="11"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="11"/>
-    </row>
-    <row r="32" spans="14:19" ht="18" x14ac:dyDescent="0.2">
-      <c r="N32" s="11"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-    </row>
-    <row r="33" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N33" s="11"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-    </row>
-    <row r="34" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N34" s="11"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-    </row>
-    <row r="35" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="O35" s="12"/>
-      <c r="R35" s="11"/>
-    </row>
-    <row r="36" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N36" s="11"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-    </row>
-    <row r="37" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N37" s="11"/>
-      <c r="O37" s="12"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-    </row>
-    <row r="38" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N38" s="11"/>
-      <c r="O38" s="12"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
-      <c r="R38" s="11"/>
-    </row>
-    <row r="39" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="O39" s="12"/>
-      <c r="R39" s="11"/>
-    </row>
-    <row r="40" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N40" s="11"/>
-      <c r="O40" s="12"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
-    </row>
-    <row r="41" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N41" s="11"/>
-      <c r="O41" s="12"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-    </row>
-    <row r="42" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N42" s="11"/>
-      <c r="O42" s="12"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
-      <c r="R42" s="11"/>
-    </row>
-    <row r="43" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N43" s="11"/>
-      <c r="O43" s="12"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-    </row>
-    <row r="44" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="O44" s="12"/>
-      <c r="P44" s="11"/>
-      <c r="R44" s="11"/>
-    </row>
-    <row r="45" spans="14:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="N45" s="11"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
+        <v>387</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2688,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -2839,10 +2418,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>48</v>
@@ -2853,10 +2432,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>60</v>
@@ -2867,24 +2446,24 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>48</v>
@@ -2895,10 +2474,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>48</v>
@@ -2909,24 +2488,24 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>48</v>
@@ -2937,57 +2516,15 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2999,1091 +2536,1093 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8.83203125" style="5"/>
-    <col min="3" max="3" width="13.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="8.83203125" style="5"/>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>120</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="5" t="b">
+      <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>90</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="5" t="b">
+      <c r="F3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>20</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="5" t="b">
+      <c r="F4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="5" t="b">
+      <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>60</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="5" t="b">
+      <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10">
+        <v>210</v>
+      </c>
+      <c r="E10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18">
+        <v>60</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23">
+        <v>200</v>
+      </c>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24">
+        <v>140</v>
+      </c>
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>302</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33">
+        <v>60</v>
+      </c>
+      <c r="E33" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="E36" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="5">
-        <v>80</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D37">
+        <v>0.5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38">
+        <v>200</v>
+      </c>
+      <c r="E38" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39">
+        <v>40</v>
+      </c>
+      <c r="E39" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>67</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>67</v>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49">
         <v>2</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E49" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="4">
+        <v>5</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F51" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B52" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D52" s="4">
+        <v>4</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="5">
-        <v>210</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="5">
-        <v>8</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="5">
-        <v>55</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="5">
-        <v>50</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="5">
-        <v>85</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="F52" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>256</v>
+      </c>
+      <c r="B53" t="s">
+        <v>264</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="F53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="5">
-        <v>60</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="5">
-        <v>25</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="5">
-        <v>50</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="5">
-        <v>30</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="5">
-        <v>200</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="5">
-        <v>140</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D26" s="5">
-        <v>4</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="5">
-        <v>2</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="5">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="5">
-        <v>150</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="5">
-        <v>100</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="5">
-        <v>20</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="5">
-        <v>1</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="5">
-        <v>60</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" s="5">
-        <v>6</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="5">
-        <v>30</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="5">
-        <v>200</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="5">
-        <v>40</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="5">
-        <v>4</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="5">
-        <v>10</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D46" s="5">
-        <v>3</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47" s="5">
-        <v>10</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48" s="5">
-        <v>1</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="5">
-        <v>3</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F49" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D50" s="5">
-        <v>2</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="5">
-        <v>1</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D52" s="5">
-        <v>5</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F52" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D53" s="5">
-        <v>4</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D54" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F54" s="5" t="b">
+      <c r="F54" s="4" t="b">
         <v>0</v>
       </c>
       <c r="I54" s="4"/>
@@ -4092,22 +3631,22 @@
       <c r="L54" s="4"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D55" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E55" s="5" t="s">
+      <c r="A55" t="s">
+        <v>256</v>
+      </c>
+      <c r="B55" t="s">
+        <v>264</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D55" s="4">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="5" t="b">
+      <c r="F55" s="4" t="b">
         <v>0</v>
       </c>
       <c r="I55" s="4"/>
@@ -4116,1606 +3655,1182 @@
       <c r="L55" s="4"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="A56" t="s">
+        <v>256</v>
+      </c>
+      <c r="B56" t="s">
+        <v>264</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D56" s="4">
         <v>4</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>256</v>
+      </c>
+      <c r="B57" t="s">
+        <v>265</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="4">
+        <v>3</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>256</v>
+      </c>
+      <c r="B58" t="s">
+        <v>265</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D58" s="4">
+        <v>3</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>256</v>
+      </c>
+      <c r="B59" t="s">
+        <v>265</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D59" s="4">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>256</v>
+      </c>
+      <c r="B60" t="s">
+        <v>265</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>256</v>
+      </c>
+      <c r="B61" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="4">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>256</v>
+      </c>
+      <c r="B62" t="s">
+        <v>265</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D62" s="4">
+        <v>2</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>256</v>
+      </c>
+      <c r="B63" t="s">
+        <v>266</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D63" s="4">
+        <v>400</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>256</v>
+      </c>
+      <c r="B64" t="s">
+        <v>266</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D57" s="5">
+      <c r="F64" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>256</v>
+      </c>
+      <c r="B65" t="s">
+        <v>266</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D65" s="4">
+        <v>1</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>256</v>
+      </c>
+      <c r="B66" t="s">
+        <v>266</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D66" s="4">
+        <v>1</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>256</v>
+      </c>
+      <c r="B67" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>256</v>
+      </c>
+      <c r="B68" t="s">
+        <v>266</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>311</v>
+      </c>
+      <c r="B69" t="s">
+        <v>314</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D69" s="4">
+        <v>200</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>311</v>
+      </c>
+      <c r="B70" t="s">
+        <v>314</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D70" s="4">
+        <v>2</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F70" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>311</v>
+      </c>
+      <c r="B71" t="s">
+        <v>314</v>
+      </c>
+      <c r="C71" t="s">
+        <v>320</v>
+      </c>
+      <c r="D71" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F71" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>311</v>
+      </c>
+      <c r="B72" t="s">
+        <v>314</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D72" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F72" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>311</v>
+      </c>
+      <c r="B73" t="s">
+        <v>314</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D73" s="4">
+        <v>3</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F73" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>311</v>
+      </c>
+      <c r="B74" t="s">
+        <v>314</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D74" s="4">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F74" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>311</v>
+      </c>
+      <c r="B75" t="s">
+        <v>314</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D75" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="F75" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>311</v>
+      </c>
+      <c r="B76" t="s">
+        <v>314</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D76" s="4">
+        <v>30</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F76" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>311</v>
+      </c>
+      <c r="B77" t="s">
+        <v>314</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D77" s="4">
+        <v>1</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F77" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>311</v>
+      </c>
+      <c r="B78" t="s">
+        <v>314</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" s="4">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F78" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" t="s">
+        <v>314</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D79" s="4">
+        <v>1</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F79" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>348</v>
+      </c>
+      <c r="B80" t="s">
+        <v>353</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D80" s="4">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F80" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>348</v>
+      </c>
+      <c r="B81" t="s">
+        <v>353</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" s="4">
+        <v>1</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F81" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>348</v>
+      </c>
+      <c r="B82" t="s">
+        <v>353</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D82" s="4">
+        <v>1</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F82" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>348</v>
+      </c>
+      <c r="B83" t="s">
+        <v>353</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D83" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F83" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>348</v>
+      </c>
+      <c r="B84" t="s">
+        <v>353</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D84" s="4">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F84" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>348</v>
+      </c>
+      <c r="B85" t="s">
+        <v>353</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D85" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F85" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>348</v>
+      </c>
+      <c r="B86" t="s">
+        <v>353</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D86" s="4">
+        <v>1</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F86" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>370</v>
+      </c>
+      <c r="B87" t="s">
+        <v>377</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D87" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F87" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>370</v>
+      </c>
+      <c r="B88" t="s">
+        <v>377</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D88" s="4">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F88" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>370</v>
+      </c>
+      <c r="B89" t="s">
+        <v>377</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D89" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F89" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>370</v>
+      </c>
+      <c r="B90" t="s">
+        <v>377</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D90" s="4">
+        <v>1</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F90" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>370</v>
+      </c>
+      <c r="B91" t="s">
+        <v>378</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D91" s="4">
         <v>4</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D58" s="5">
-        <v>3</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D59" s="5">
-        <v>3</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D60" s="5">
-        <v>1</v>
-      </c>
-      <c r="E60" s="5" t="s">
+      <c r="E91" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F91" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>370</v>
+      </c>
+      <c r="B92" t="s">
+        <v>378</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D92" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F92" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>370</v>
+      </c>
+      <c r="B93" t="s">
+        <v>378</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D93" s="4">
+        <v>1</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F93" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>370</v>
+      </c>
+      <c r="B94" t="s">
+        <v>378</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D94" s="4">
+        <v>5</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D61" s="5">
-        <v>1</v>
-      </c>
-      <c r="E61" s="5" t="s">
+      <c r="F94" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>370</v>
+      </c>
+      <c r="B95" t="s">
+        <v>378</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D95" s="4">
+        <v>10</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F61" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="F95" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>370</v>
+      </c>
+      <c r="B96" t="s">
+        <v>378</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D96" s="4">
+        <v>2</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F96" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>370</v>
+      </c>
+      <c r="B97" t="s">
+        <v>378</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+      <c r="E97" t="s">
+        <v>75</v>
+      </c>
+      <c r="F97" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>370</v>
+      </c>
+      <c r="B98" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="5">
-        <v>1</v>
-      </c>
-      <c r="E62" s="5" t="s">
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98" t="s">
         <v>67</v>
       </c>
-      <c r="F62" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D63" s="5">
+      <c r="F98" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>370</v>
+      </c>
+      <c r="B99" t="s">
+        <v>378</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99" t="s">
+        <v>67</v>
+      </c>
+      <c r="F99" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>370</v>
+      </c>
+      <c r="B100" t="s">
+        <v>388</v>
+      </c>
+      <c r="C100" t="s">
+        <v>403</v>
+      </c>
+      <c r="D100" s="4">
+        <v>1</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="F100" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>382</v>
+      </c>
+      <c r="B101" t="s">
+        <v>388</v>
+      </c>
+      <c r="C101" t="s">
+        <v>403</v>
+      </c>
+      <c r="D101" s="4">
+        <v>1</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="F101" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>382</v>
+      </c>
+      <c r="B102" t="s">
+        <v>388</v>
+      </c>
+      <c r="C102" t="s">
+        <v>404</v>
+      </c>
+      <c r="D102" s="4">
+        <v>80</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F102" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>382</v>
+      </c>
+      <c r="B103" t="s">
+        <v>388</v>
+      </c>
+      <c r="C103" t="s">
+        <v>392</v>
+      </c>
+      <c r="D103" s="4">
         <v>2</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E103" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="F103" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>382</v>
+      </c>
+      <c r="B104" t="s">
+        <v>388</v>
+      </c>
+      <c r="C104" t="s">
+        <v>394</v>
+      </c>
+      <c r="D104" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F104" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>382</v>
+      </c>
+      <c r="B105" t="s">
+        <v>388</v>
+      </c>
+      <c r="C105" t="s">
+        <v>405</v>
+      </c>
+      <c r="D105" s="4">
+        <v>1</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F105" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>382</v>
+      </c>
+      <c r="B106" t="s">
+        <v>388</v>
+      </c>
+      <c r="C106" t="s">
+        <v>317</v>
+      </c>
+      <c r="D106" s="4">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F106" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>382</v>
+      </c>
+      <c r="B107" t="s">
+        <v>388</v>
+      </c>
+      <c r="C107" t="s">
+        <v>406</v>
+      </c>
+      <c r="D107" s="4">
+        <v>1</v>
+      </c>
+      <c r="E107" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="F107" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>382</v>
+      </c>
+      <c r="B108" t="s">
+        <v>388</v>
+      </c>
+      <c r="C108" t="s">
+        <v>398</v>
+      </c>
+      <c r="D108" s="4">
+        <v>5</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F108" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>382</v>
+      </c>
+      <c r="B109" t="s">
+        <v>388</v>
+      </c>
+      <c r="C109" t="s">
         <v>400</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="D109" s="4">
+        <v>4</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F109" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>382</v>
+      </c>
+      <c r="B110" t="s">
+        <v>388</v>
+      </c>
+      <c r="C110" t="s">
+        <v>402</v>
+      </c>
+      <c r="D110" s="4">
+        <v>1</v>
+      </c>
+      <c r="E110" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D65" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E65" s="5" t="s">
+      <c r="F110" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>382</v>
+      </c>
+      <c r="B111" t="s">
+        <v>388</v>
+      </c>
+      <c r="C111" t="s">
+        <v>409</v>
+      </c>
+      <c r="D111" s="4">
+        <v>6</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F65" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D66" s="5">
-        <v>1</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="F111" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>382</v>
+      </c>
+      <c r="B112" t="s">
+        <v>388</v>
+      </c>
+      <c r="C112" t="s">
+        <v>411</v>
+      </c>
+      <c r="D112">
+        <v>6</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F112" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>382</v>
+      </c>
+      <c r="B113" t="s">
+        <v>388</v>
+      </c>
+      <c r="C113" t="s">
+        <v>89</v>
+      </c>
+      <c r="D113" s="4">
+        <v>1</v>
+      </c>
+      <c r="E113" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F66" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D67" s="5">
-        <v>1</v>
-      </c>
-      <c r="E67" s="5" t="s">
+      <c r="F113" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>382</v>
+      </c>
+      <c r="B114" t="s">
+        <v>388</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D114" s="4">
+        <v>1</v>
+      </c>
+      <c r="E114" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D68" s="5">
-        <v>1</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F68" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" s="5">
-        <v>1</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F69" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D70" s="5">
-        <v>200</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F70" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D71" s="5">
-        <v>2</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F71" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D72" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F72" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D73" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F73" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D74" s="5">
-        <v>3</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F74" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="D75" s="5">
-        <v>1</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F75" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="D76" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="F76" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D77" s="5">
-        <v>30</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F77" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="D78" s="5">
-        <v>1</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F78" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D79" s="5">
-        <v>1</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F79" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D80" s="5">
-        <v>1</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F80" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D81" s="5">
-        <v>1</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F81" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D82" s="5">
-        <v>1</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F82" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D83" s="5">
-        <v>1</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F83" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="D84" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F84" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D85" s="5">
-        <v>1</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F85" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D86" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F86" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D87" s="5">
-        <v>1</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F87" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="D88" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F88" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D89" s="5">
-        <v>1</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F89" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D90" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F90" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D91" s="5">
-        <v>1</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F91" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="D92" s="5">
-        <v>4</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F92" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D93" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F93" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D94" s="5">
-        <v>1</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F94" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A95" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="D95" s="5">
-        <v>5</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F95" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="D96" s="5">
-        <v>10</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F96" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D97" s="5">
-        <v>2</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F97" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D98" s="5">
-        <v>2</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F98" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D99" s="5">
-        <v>1</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F99" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D100" s="5">
-        <v>1</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F100" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="D101" s="5">
-        <v>1</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="F101" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="D102" s="5">
-        <v>1</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="F102" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D103" s="5">
-        <v>80</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F103" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A104" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="D104" s="5">
-        <v>2</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="F104" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A105" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D105" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F105" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A106" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D106" s="5">
-        <v>1</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F106" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D107" s="5">
-        <v>1</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F107" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A108" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D108" s="5">
-        <v>1</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F108" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A109" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D109" s="5">
-        <v>5</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F109" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A110" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="D110" s="5">
-        <v>4</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F110" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A111" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="D111" s="5">
-        <v>1</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F111" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="D112" s="5">
-        <v>6</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F112" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D113" s="5">
-        <v>6</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F113" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D114" s="5">
-        <v>1</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F114" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A115" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D115" s="5">
-        <v>1</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F115" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A116" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D116" s="5">
-        <v>40</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F116" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A117" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="D117" s="5">
-        <v>60</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F117" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D118" s="5">
-        <v>100</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F118" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A119" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="D119" s="5">
-        <v>10</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F119" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A120" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D120" s="5">
-        <v>1</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F120" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A121" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="D121" s="5">
-        <v>10</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F121" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A122" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D122" s="5">
-        <v>4</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F122" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="D123" s="5">
-        <v>24</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F123" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A124" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D124" s="5">
-        <v>40</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F124" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A125" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D125" s="5">
-        <v>1</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F125" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A126" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C126" t="s">
-        <v>487</v>
-      </c>
-      <c r="D126" s="5">
-        <v>2</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F126" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C127" t="s">
-        <v>488</v>
-      </c>
-      <c r="D127" s="5">
-        <v>2</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F127" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C128" t="s">
-        <v>489</v>
-      </c>
-      <c r="D128" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F128" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C129" t="s">
-        <v>490</v>
-      </c>
-      <c r="D129" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F129" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C130" t="s">
-        <v>268</v>
-      </c>
-      <c r="D130" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F130" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C131" t="s">
-        <v>293</v>
-      </c>
-      <c r="D131" s="5">
-        <v>2</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F131" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C132" t="s">
-        <v>87</v>
-      </c>
-      <c r="D132" s="5">
-        <v>1</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F132" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C133" t="s">
-        <v>94</v>
-      </c>
-      <c r="D133" s="5">
-        <v>1</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F133" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C134" t="s">
-        <v>491</v>
-      </c>
-      <c r="D134" s="5">
-        <v>1</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F134" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D135" s="5">
-        <v>1</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F135" s="5" t="b">
+      <c r="F114" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5726,7 +4841,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -5899,10 +5014,10 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B22" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -5979,34 +5094,34 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B32" t="s">
         <v>267</v>
-      </c>
-      <c r="B32" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>277</v>
+      </c>
+      <c r="B33" t="s">
         <v>268</v>
-      </c>
-      <c r="B33" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" t="s">
         <v>269</v>
-      </c>
-      <c r="B34" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>279</v>
+      </c>
+      <c r="B35" t="s">
         <v>270</v>
-      </c>
-      <c r="B35" t="s">
-        <v>261</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -6027,10 +5142,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" t="s">
         <v>271</v>
-      </c>
-      <c r="B37" t="s">
-        <v>262</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -6039,58 +5154,58 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -6099,40 +5214,40 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B45" t="s">
         <v>268</v>
-      </c>
-      <c r="B45" t="s">
-        <v>259</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="G48" s="2"/>
       <c r="I48" s="4"/>
@@ -6140,236 +5255,164 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>405</v>
+      </c>
+      <c r="B57" t="s">
         <v>395</v>
-      </c>
-      <c r="B57" t="s">
-        <v>385</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>406</v>
+      </c>
+      <c r="B58" t="s">
         <v>396</v>
-      </c>
-      <c r="B58" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="B59" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B61" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B65" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="B67" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="B68" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="B69" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B70" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>487</v>
-      </c>
-      <c r="B71" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>488</v>
-      </c>
-      <c r="B72" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>489</v>
-      </c>
-      <c r="B73" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>490</v>
-      </c>
-      <c r="B74" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>491</v>
-      </c>
-      <c r="B75" t="s">
-        <v>496</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -6382,7 +5425,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -6415,10 +5458,10 @@
         <v>124</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6435,7 +5478,7 @@
         <v>43</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>146</v>
@@ -6461,7 +5504,7 @@
         <v>43</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>147</v>
@@ -6487,7 +5530,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>148</v>
@@ -6513,7 +5556,7 @@
         <v>43</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>149</v>
@@ -6539,10 +5582,10 @@
         <v>46</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>514</v>
+        <v>157</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>510</v>
+        <v>150</v>
       </c>
       <c r="G6" s="4">
         <v>5</v>
@@ -6565,10 +5608,10 @@
         <v>46</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>516</v>
+        <v>158</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>511</v>
+        <v>151</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
@@ -6591,10 +5634,10 @@
         <v>46</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>515</v>
+        <v>159</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>512</v>
+        <v>152</v>
       </c>
       <c r="G8" s="4">
         <v>10</v>
@@ -6617,10 +5660,10 @@
         <v>144</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>517</v>
+        <v>160</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>513</v>
+        <v>153</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -6643,10 +5686,10 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G10" s="4">
         <v>3</v>
@@ -6669,10 +5712,10 @@
         <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G11" s="4">
         <v>5</v>
@@ -6695,10 +5738,10 @@
         <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G12" s="4">
         <v>2</v>
@@ -6721,10 +5764,10 @@
         <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G13" s="4">
         <v>5</v>
@@ -6747,10 +5790,10 @@
         <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G14" s="4">
         <v>3</v>
@@ -6773,10 +5816,10 @@
         <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G15" s="4">
         <v>2</v>
@@ -6799,10 +5842,10 @@
         <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G16" s="4">
         <v>1</v>
@@ -6825,10 +5868,10 @@
         <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G17" s="4">
         <v>20</v>
@@ -6851,10 +5894,10 @@
         <v>52</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G18" s="4">
         <v>5</v>
@@ -6877,10 +5920,10 @@
         <v>52</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G19" s="4">
         <v>3</v>
@@ -6903,10 +5946,10 @@
         <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G20" s="4">
         <v>10</v>
@@ -6929,10 +5972,10 @@
         <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G21" s="4">
         <v>1</v>
@@ -6955,10 +5998,10 @@
         <v>55</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G22" s="4">
         <v>3</v>
@@ -6981,10 +6024,10 @@
         <v>55</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G23" s="4">
         <v>1</v>
@@ -7007,10 +6050,10 @@
         <v>55</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G24" s="4">
         <v>1</v>
@@ -7038,10 +6081,10 @@
         <v>55</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F25" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G25" s="4">
         <v>5</v>
@@ -7064,10 +6107,10 @@
         <v>55</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G26" s="4">
         <v>3</v>
@@ -7090,10 +6133,10 @@
         <v>55</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
@@ -7116,10 +6159,10 @@
         <v>55</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G28" s="4">
         <v>65</v>
@@ -7142,10 +6185,10 @@
         <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G29" s="4">
         <v>0</v>
@@ -7168,10 +6211,10 @@
         <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
@@ -7194,10 +6237,10 @@
         <v>43</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G31" s="4">
         <v>3</v>
@@ -7220,10 +6263,10 @@
         <v>43</v>
       </c>
       <c r="E32" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="G32" s="4">
         <v>60</v>
@@ -7246,10 +6289,10 @@
         <v>46</v>
       </c>
       <c r="E33" t="s">
+        <v>236</v>
+      </c>
+      <c r="F33" t="s">
         <v>228</v>
-      </c>
-      <c r="F33" t="s">
-        <v>220</v>
       </c>
       <c r="G33" s="4">
         <v>5</v>
@@ -7272,10 +6315,10 @@
         <v>46</v>
       </c>
       <c r="E34" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" t="s">
         <v>229</v>
-      </c>
-      <c r="F34" t="s">
-        <v>221</v>
       </c>
       <c r="G34" s="4">
         <v>3</v>
@@ -7298,10 +6341,10 @@
         <v>49</v>
       </c>
       <c r="E35" t="s">
+        <v>238</v>
+      </c>
+      <c r="F35" t="s">
         <v>230</v>
-      </c>
-      <c r="F35" t="s">
-        <v>222</v>
       </c>
       <c r="G35" s="4">
         <v>3</v>
@@ -7324,10 +6367,10 @@
         <v>49</v>
       </c>
       <c r="E36" t="s">
+        <v>239</v>
+      </c>
+      <c r="F36" t="s">
         <v>231</v>
-      </c>
-      <c r="F36" t="s">
-        <v>223</v>
       </c>
       <c r="G36" s="4">
         <v>5</v>
@@ -7350,10 +6393,10 @@
         <v>49</v>
       </c>
       <c r="E37" t="s">
+        <v>240</v>
+      </c>
+      <c r="F37" t="s">
         <v>232</v>
-      </c>
-      <c r="F37" t="s">
-        <v>224</v>
       </c>
       <c r="G37" s="4">
         <v>2</v>
@@ -7376,10 +6419,10 @@
         <v>49</v>
       </c>
       <c r="E38" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" t="s">
         <v>233</v>
-      </c>
-      <c r="F38" t="s">
-        <v>225</v>
       </c>
       <c r="G38" s="4">
         <v>25</v>
@@ -7402,10 +6445,10 @@
         <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="F39" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="G39" s="4">
         <v>10</v>
@@ -7428,10 +6471,10 @@
         <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>482</v>
+        <v>308</v>
       </c>
       <c r="F40" t="s">
-        <v>481</v>
+        <v>251</v>
       </c>
       <c r="G40" s="4">
         <v>50</v>
@@ -7454,10 +6497,10 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F41" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="G41" s="4">
         <v>5</v>
@@ -7480,10 +6523,10 @@
         <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="F42" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="G42" s="9">
         <v>5</v>
@@ -7506,10 +6549,10 @@
         <v>49</v>
       </c>
       <c r="E43" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F43" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="G43" s="9">
         <v>1</v>
@@ -7520,22 +6563,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B44" s="4">
         <v>1</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="E44" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="F44" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="G44" s="9">
         <v>5</v>
@@ -7546,22 +6589,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B45" s="4">
         <v>2</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="E45" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F45" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G45" s="9">
         <v>5</v>
@@ -7572,22 +6615,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="E46" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F46" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G46" s="9">
         <v>3</v>
@@ -7598,7 +6641,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B47" s="4">
         <v>4</v>
@@ -7610,10 +6653,10 @@
         <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="F47" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G47" s="9">
         <v>2</v>
@@ -7624,7 +6667,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B48" s="4">
         <v>5</v>
@@ -7636,10 +6679,10 @@
         <v>49</v>
       </c>
       <c r="E48" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="F48" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G48" s="9">
         <v>3</v>
@@ -7650,7 +6693,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B49" s="4">
         <v>6</v>
@@ -7662,10 +6705,10 @@
         <v>49</v>
       </c>
       <c r="E49" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F49" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="G49" s="9">
         <v>5</v>
@@ -7676,7 +6719,7 @@
     </row>
     <row r="50" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B50" s="4">
         <v>7</v>
@@ -7688,10 +6731,10 @@
         <v>49</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="G50" s="9">
         <v>10</v>
@@ -7702,7 +6745,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B51" s="4">
         <v>8</v>
@@ -7714,10 +6757,10 @@
         <v>49</v>
       </c>
       <c r="E51" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F51" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="G51" s="9">
         <v>5</v>
@@ -7728,7 +6771,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
@@ -7740,10 +6783,10 @@
         <v>49</v>
       </c>
       <c r="E52" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F52" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="G52" s="9">
         <v>10</v>
@@ -7754,7 +6797,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B53" s="4">
         <v>2</v>
@@ -7766,10 +6809,10 @@
         <v>49</v>
       </c>
       <c r="E53" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F53" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G53" s="9">
         <v>10</v>
@@ -7780,7 +6823,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B54" s="4">
         <v>3</v>
@@ -7792,10 +6835,10 @@
         <v>49</v>
       </c>
       <c r="E54" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F54" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="G54" s="9">
         <v>5</v>
@@ -7806,7 +6849,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B55" s="4">
         <v>4</v>
@@ -7818,10 +6861,10 @@
         <v>49</v>
       </c>
       <c r="E55" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="F55" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="G55" s="9">
         <v>10</v>
@@ -7832,7 +6875,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B56" s="4">
         <v>5</v>
@@ -7844,10 +6887,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F56" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="G56" s="9">
         <v>5</v>
@@ -7858,7 +6901,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B57" s="4">
         <v>6</v>
@@ -7870,10 +6913,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F57" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="G57" s="9">
         <v>1</v>
@@ -7884,7 +6927,7 @@
     </row>
     <row r="58" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B58" s="4">
         <v>7</v>
@@ -7896,10 +6939,10 @@
         <v>49</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="G58" s="9">
         <v>20</v>
@@ -7910,7 +6953,7 @@
     </row>
     <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B59" s="4">
         <v>1</v>
@@ -7922,10 +6965,10 @@
         <v>49</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="G59" s="9">
         <v>10</v>
@@ -7936,7 +6979,7 @@
     </row>
     <row r="60" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B60" s="4">
         <v>2</v>
@@ -7948,10 +6991,10 @@
         <v>49</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="G60" s="9">
         <v>1</v>
@@ -7962,7 +7005,7 @@
     </row>
     <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B61" s="4">
         <v>3</v>
@@ -7974,10 +7017,10 @@
         <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G61" s="9">
         <v>20</v>
@@ -7988,7 +7031,7 @@
     </row>
     <row r="62" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B62" s="4">
         <v>4</v>
@@ -8000,10 +7043,10 @@
         <v>49</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="G62" s="9">
         <v>1</v>
@@ -8014,7 +7057,7 @@
     </row>
     <row r="63" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B63" s="4">
         <v>1</v>
@@ -8023,13 +7066,13 @@
         <v>60</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="G63" s="9">
         <v>32</v>
@@ -8040,7 +7083,7 @@
     </row>
     <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B64" s="4">
         <v>1</v>
@@ -8052,10 +7095,10 @@
         <v>49</v>
       </c>
       <c r="E64" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="G64" s="9">
         <v>10</v>
@@ -8066,7 +7109,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B65" s="4">
         <v>2</v>
@@ -8078,10 +7121,10 @@
         <v>49</v>
       </c>
       <c r="E65" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="F65" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="G65" s="9">
         <v>5</v>
@@ -8092,7 +7135,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B66" s="4">
         <v>3</v>
@@ -8104,10 +7147,10 @@
         <v>49</v>
       </c>
       <c r="E66" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F66" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="G66" s="9">
         <v>3</v>
@@ -8118,7 +7161,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B67" s="4">
         <v>4</v>
@@ -8130,10 +7173,10 @@
         <v>49</v>
       </c>
       <c r="E67" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F67" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G67" s="9">
         <v>3</v>
@@ -8144,7 +7187,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B68" s="4">
         <v>5</v>
@@ -8156,10 +7199,10 @@
         <v>49</v>
       </c>
       <c r="E68" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F68" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="G68" s="9">
         <v>3</v>
@@ -8170,7 +7213,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B69" s="4">
         <v>6</v>
@@ -8182,10 +7225,10 @@
         <v>49</v>
       </c>
       <c r="E69" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="F69" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G69" s="4">
         <v>1</v>
@@ -8196,7 +7239,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B70" s="4">
         <v>7</v>
@@ -8208,10 +7251,10 @@
         <v>49</v>
       </c>
       <c r="E70" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="F70" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="G70" s="4">
         <v>20</v>
@@ -8222,7 +7265,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B71" s="4">
         <v>8</v>
@@ -8234,10 +7277,10 @@
         <v>49</v>
       </c>
       <c r="E71" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F71" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -8248,7 +7291,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B72" s="4">
         <v>9</v>
@@ -8260,10 +7303,10 @@
         <v>49</v>
       </c>
       <c r="E72" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="F72" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="G72" s="4">
         <v>0</v>
@@ -8274,7 +7317,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B73" s="4">
         <v>10</v>
@@ -8286,10 +7329,10 @@
         <v>49</v>
       </c>
       <c r="E73" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F73" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="G73" s="4">
         <v>1</v>
@@ -8300,7 +7343,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B74" s="4">
         <v>1</v>
@@ -8312,10 +7355,10 @@
         <v>49</v>
       </c>
       <c r="E74" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F74" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="G74" s="9">
         <v>50</v>
@@ -8326,7 +7369,7 @@
     </row>
     <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B75" s="4">
         <v>2</v>
@@ -8338,10 +7381,10 @@
         <v>49</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F75" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="G75" s="9">
         <v>10</v>
@@ -8352,7 +7395,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B76" s="4">
         <v>3</v>
@@ -8364,10 +7407,10 @@
         <v>49</v>
       </c>
       <c r="E76" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F76" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="G76" s="9">
         <v>10</v>
@@ -8378,7 +7421,7 @@
     </row>
     <row r="77" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B77" s="4">
         <v>4</v>
@@ -8390,10 +7433,10 @@
         <v>49</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F77" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G77" s="9">
         <v>10</v>
@@ -8404,7 +7447,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B78" s="4">
         <v>5</v>
@@ -8416,10 +7459,10 @@
         <v>49</v>
       </c>
       <c r="E78" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F78" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="G78" s="9">
         <v>10</v>
@@ -8430,7 +7473,7 @@
     </row>
     <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B79" s="4">
         <v>6</v>
@@ -8442,10 +7485,10 @@
         <v>49</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="F79" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="G79" s="9">
         <v>1</v>
@@ -8456,7 +7499,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B80" s="4">
         <v>7</v>
@@ -8468,379 +7511,15 @@
         <v>49</v>
       </c>
       <c r="E80" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="F80" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G80" s="9">
         <v>1</v>
       </c>
       <c r="H80" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A81" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B81" s="4">
-        <v>1</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="G81" s="9">
-        <v>5</v>
-      </c>
-      <c r="H81" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B82" s="4">
-        <v>2</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E82" t="s">
-        <v>473</v>
-      </c>
-      <c r="F82" t="s">
-        <v>465</v>
-      </c>
-      <c r="G82" s="9">
-        <v>30</v>
-      </c>
-      <c r="H82" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B83" s="4">
-        <v>3</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="F83" t="s">
-        <v>466</v>
-      </c>
-      <c r="G83" s="9">
-        <v>1</v>
-      </c>
-      <c r="H83" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B84" s="4">
-        <v>4</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E84" t="s">
-        <v>475</v>
-      </c>
-      <c r="F84" t="s">
-        <v>467</v>
-      </c>
-      <c r="G84" s="9">
-        <v>5</v>
-      </c>
-      <c r="H84" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A85" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B85" s="4">
-        <v>5</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="F85" t="s">
-        <v>468</v>
-      </c>
-      <c r="G85" s="9">
-        <v>1</v>
-      </c>
-      <c r="H85" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A86" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B86" s="4">
-        <v>6</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="G86" s="9">
-        <v>3</v>
-      </c>
-      <c r="H86" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A87" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B87" s="4">
-        <v>7</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="F87" t="s">
-        <v>470</v>
-      </c>
-      <c r="G87" s="9">
-        <v>40</v>
-      </c>
-      <c r="H87" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B88" s="4">
-        <v>8</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="F88" t="s">
-        <v>471</v>
-      </c>
-      <c r="G88" s="9">
-        <v>0</v>
-      </c>
-      <c r="H88" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B89" s="4">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E89" t="s">
-        <v>504</v>
-      </c>
-      <c r="F89" t="s">
-        <v>498</v>
-      </c>
-      <c r="G89" s="9">
-        <v>3</v>
-      </c>
-      <c r="H89" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B90" s="4">
-        <v>2</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E90" t="s">
-        <v>505</v>
-      </c>
-      <c r="F90" t="s">
-        <v>499</v>
-      </c>
-      <c r="G90" s="9">
-        <v>5</v>
-      </c>
-      <c r="H90" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B91" s="4">
-        <v>3</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E91" t="s">
-        <v>506</v>
-      </c>
-      <c r="F91" t="s">
-        <v>500</v>
-      </c>
-      <c r="G91" s="9">
-        <v>1</v>
-      </c>
-      <c r="H91" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B92" s="4">
-        <v>4</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E92" t="s">
-        <v>507</v>
-      </c>
-      <c r="F92" t="s">
-        <v>501</v>
-      </c>
-      <c r="G92" s="4">
-        <v>3</v>
-      </c>
-      <c r="H92" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B93" s="4">
-        <v>5</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E93" t="s">
-        <v>508</v>
-      </c>
-      <c r="F93" t="s">
-        <v>502</v>
-      </c>
-      <c r="G93" s="4">
-        <v>5</v>
-      </c>
-      <c r="H93" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B94" s="4">
-        <v>6</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E94" t="s">
-        <v>509</v>
-      </c>
-      <c r="F94" t="s">
-        <v>503</v>
-      </c>
-      <c r="G94" s="9">
-        <v>3</v>
-      </c>
-      <c r="H94" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8852,16 +7531,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BD390-6058-3244-B040-3ECD44D7EDBB}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
     <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -8869,10 +7543,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D1" t="s">
         <v>65</v>
@@ -8883,10 +7557,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -8897,10 +7571,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -8911,10 +7585,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -8925,10 +7599,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -8939,10 +7613,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -8953,10 +7627,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -8967,10 +7641,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -8981,10 +7655,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -8995,10 +7669,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -9009,10 +7683,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -9023,10 +7697,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -9037,10 +7711,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -9051,10 +7725,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -9065,10 +7739,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -9079,10 +7753,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -9093,10 +7767,10 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C17" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -9107,10 +7781,10 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C18" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -9121,10 +7795,10 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -9135,10 +7809,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -9149,10 +7823,10 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -9163,10 +7837,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -9177,10 +7851,10 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -9191,10 +7865,10 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -9205,10 +7879,10 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -9219,10 +7893,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -9233,10 +7907,10 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -9247,10 +7921,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -9261,10 +7935,10 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -9275,10 +7949,10 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -9286,13 +7960,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" t="s">
         <v>247</v>
       </c>
-      <c r="B31" t="s">
-        <v>239</v>
-      </c>
       <c r="C31" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -9300,249 +7974,143 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35" t="s">
+        <v>166</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B36" t="s">
+        <v>331</v>
+      </c>
+      <c r="C36" t="s">
+        <v>332</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B37" t="s">
+        <v>174</v>
+      </c>
+      <c r="C37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B38" t="s">
+        <v>364</v>
+      </c>
+      <c r="C38" t="s">
+        <v>366</v>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B39" t="s">
+        <v>367</v>
+      </c>
+      <c r="C39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B40" t="s">
         <v>247</v>
       </c>
-      <c r="B32" t="s">
-        <v>190</v>
-      </c>
-      <c r="C32" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B33" t="s">
-        <v>166</v>
-      </c>
-      <c r="C33" t="s">
-        <v>159</v>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B34" t="s">
-        <v>165</v>
-      </c>
-      <c r="C34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B35" t="s">
-        <v>165</v>
-      </c>
-      <c r="C35" t="s">
-        <v>158</v>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B36" t="s">
-        <v>321</v>
-      </c>
-      <c r="C36" t="s">
-        <v>322</v>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B37" t="s">
-        <v>166</v>
-      </c>
-      <c r="C37" t="s">
-        <v>159</v>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B38" t="s">
-        <v>354</v>
-      </c>
-      <c r="C38" t="s">
-        <v>356</v>
-      </c>
-      <c r="D38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B39" t="s">
-        <v>357</v>
-      </c>
-      <c r="C39" t="s">
-        <v>355</v>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B40" t="s">
-        <v>239</v>
-      </c>
       <c r="C40" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D40" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C41" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D41" t="b">
         <v>0</v>
       </c>
-      <c r="N41" s="14"/>
-    </row>
-    <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B42" t="s">
-        <v>190</v>
-      </c>
-      <c r="C42" t="s">
-        <v>189</v>
-      </c>
-      <c r="D42" t="b">
-        <v>0</v>
-      </c>
-      <c r="N42" s="14"/>
-    </row>
-    <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B43" t="s">
-        <v>460</v>
-      </c>
-      <c r="C43" t="s">
-        <v>461</v>
-      </c>
-      <c r="D43" t="b">
-        <v>0</v>
-      </c>
-      <c r="N43" s="14"/>
-    </row>
-    <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B44" t="s">
-        <v>166</v>
-      </c>
-      <c r="C44" t="s">
-        <v>159</v>
-      </c>
-      <c r="D44" t="b">
-        <v>0</v>
-      </c>
-      <c r="N44" s="14"/>
-    </row>
-    <row r="45" spans="1:14" ht="16" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B45" t="s">
-        <v>463</v>
-      </c>
-      <c r="C45" t="s">
-        <v>462</v>
-      </c>
-      <c r="D45" t="b">
-        <v>1</v>
-      </c>
-      <c r="N45" s="14"/>
-    </row>
-    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B46" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" t="s">
-        <v>157</v>
-      </c>
-      <c r="D46" t="b">
-        <v>0</v>
-      </c>
-      <c r="N46" s="14"/>
-    </row>
-    <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B47" t="s">
-        <v>239</v>
-      </c>
-      <c r="C47" t="s">
-        <v>240</v>
-      </c>
-      <c r="D47" t="b">
-        <v>0</v>
-      </c>
-      <c r="N47" s="14"/>
-    </row>
-    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B48" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" t="s">
-        <v>159</v>
-      </c>
-      <c r="D48" t="b">
-        <v>0</v>
-      </c>
-      <c r="N48" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
